--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1618,30 +1618,89 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>E05 Venue Catalogue &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Mark a venue temporarily unavailable over existing bookings</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
+New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Unavailability recorded with a reason
+Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
+Scenario 2 - Overlapping bookings become Conflicting, not released
+Given the venue has a Pending request and a Confirmed booking inside the period When I save the unavailability Then the save succeeds, both bookings are marked Conflicting, neither is released or cancelled, and the two affected events are listed to me on save
+Scenario 3 - The event itself is untouched
+Given a Confirmed event's booking has just become Conflicting When anyone views that event Then its status is still Confirmed, every other arrangement is intact, and a venue-conflict flag with the reason category is shown; the event changes status only when its Coordinator acts (assumes O-24)
+Scenario 4 - Affected Coordinators informed
+Given the unavailability made one or more bookings Conflicting When it is saved Then the Coordinator of each affected event receives an in-app and email notification naming the venue, the period, the reason category and the event, and stating that alternative arrangements are required (assumes O-25)
+Scenario 5 - End date required and extendable
+Given I am recording an unavailability When I omit the end date and time Then the save is refused; and Given a saved unavailability When I extend its end Then bookings newly inside the longer period are handled as in Scenario 2 (assumes O-23)
+Scenario 6 - Unavailability shortened or ended early
+Given a booking is Conflicting only because of an unavailability When I shorten or end that unavailability so the booking no longer overlaps it Then the Conflicting flag clears and the booking stands as it was; a booking the Coordinator has already cancelled or replaced is not restored (assumes O-26)
+Checklist
+- Mark a venue unavailable for a period with a reason category and a note, including when Pending or Confirmed bookings fall inside the period
+- See the affected events listed on save and their bookings marked Conflicting, with none released or cancelled
+- Confirm the affected events keep their status and other arrangements, with a visible venue-conflict flag
+- Confirm each affected Coordinator is notified in-app and by email
+- Be refused an unavailability with no end date and time
+- Confirm shortening or ending an unavailability clears the Conflicting flag on bookings it no longer touches
+- Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -1662,43 +1721,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>B-08, C-65, T-66</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -1716,43 +1775,43 @@
 - Confirm suitability is advisory and does not itself block a booking request</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-21, B-08</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -1774,43 +1833,43 @@
 - View the status of each of my booking requests</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -1830,43 +1889,43 @@
 - Confirm the Coordinator is notified of either decision</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative and the hold is recorded against my event
@@ -1887,43 +1946,43 @@
 - Confirm only one active hold or confirmed booking exists per venue and period</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -1942,43 +2001,43 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -1995,43 +2054,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2047,43 +2106,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2099,43 +2158,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2154,43 +2213,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2203,43 +2262,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2255,43 +2314,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2310,43 +2369,43 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event confirmed
 Given the event has a confirmed venue booking and its full requested equipment reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details
@@ -2369,43 +2428,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a confirmed event to planning when an arrangement breaks so that its status reflects reality.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reverted with a recorded reason
 Given an event is Confirmed When I revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -2421,43 +2480,43 @@
 - Confirm the reversion is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -2475,43 +2534,43 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -2530,43 +2589,43 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -2587,43 +2646,43 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -2642,43 +2701,43 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -2697,43 +2756,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -2745,43 +2804,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -2797,43 +2856,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -2851,43 +2910,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -2906,43 +2965,43 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has a confirmed venue When its expected attendance is increased beyond that venue's capacity Then the venue booking is flagged for review and the Venue Staff are notified
@@ -2963,43 +3022,43 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -3018,43 +3077,98 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>E10 Changes, Rescheduling &amp; Cancellation</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Handle a venue lost from a confirmed event</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lost venue flags the event
+Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
+Scenario 2 - Flagged event offers a replacement search
+Given my event is flagged When I open it Then the reason category, the period and the affected booking are shown, the original venue, dates and requirements are preserved, and I can start a venue search (E06-S01) for the same event from that screen
+Scenario 3 - Replacement requested without losing the original
+Given I have found a replacement venue When I submit a booking request for it (E06-S03) Then the request is created for the same event alongside the Conflicting booking, and I may cancel the Conflicting booking explicitly once the replacement is Confirmed; nothing is cancelled for me
+Scenario 4 - Organiser and Attendees told on the actual change
+Given I confirm a replacement venue When the venue of a Confirmed event changes Then the Organiser and registered Attendees are notified of the new venue through the existing venue-change routing (E11-S01), and not earlier (assumes O-25)
+Checklist
+- Be notified when a venue I have booked is marked unavailable over my booking
+- See the reason, period and affected booking on the event, with the original event information intact
+- Start a venue search for the same event from the flagged event
+- Request a replacement venue while the Conflicting booking remains on the event until I cancel it
+- Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3082,43 +3196,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -3138,15 +3252,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -3163,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4620,25 +4734,80 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>E05 Venue Catalogue &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Mark a venue temporarily unavailable over existing bookings</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
+New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Unavailability recorded with a reason
+Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
+Scenario 2 - Overlapping bookings become Conflicting, not released
+Given the venue has a Pending request and a Confirmed booking inside the period When I save the unavailability Then the save succeeds, both bookings are marked Conflicting, neither is released or cancelled, and the two affected events are listed to me on save
+Scenario 3 - The event itself is untouched
+Given a Confirmed event's booking has just become Conflicting When anyone views that event Then its status is still Confirmed, every other arrangement is intact, and a venue-conflict flag with the reason category is shown; the event changes status only when its Coordinator acts (assumes O-24)
+Scenario 4 - Affected Coordinators informed
+Given the unavailability made one or more bookings Conflicting When it is saved Then the Coordinator of each affected event receives an in-app and email notification naming the venue, the period, the reason category and the event, and stating that alternative arrangements are required (assumes O-25)
+Scenario 5 - End date required and extendable
+Given I am recording an unavailability When I omit the end date and time Then the save is refused; and Given a saved unavailability When I extend its end Then bookings newly inside the longer period are handled as in Scenario 2 (assumes O-23)
+Scenario 6 - Unavailability shortened or ended early
+Given a booking is Conflicting only because of an unavailability When I shorten or end that unavailability so the booking no longer overlaps it Then the Conflicting flag clears and the booking stands as it was; a booking the Coordinator has already cancelled or replaced is not restored (assumes O-26)
+Checklist
+- Mark a venue unavailable for a period with a reason category and a note, including when Pending or Confirmed bookings fall inside the period
+- See the affected events listed on save and their bookings marked Conflicting, with none released or cancelled
+- Confirm the affected events keep their status and other arrangements, with a visible venue-conflict flag
+- Confirm each affected Coordinator is notified in-app and by email
+- Be refused an unavailability with no end date and time
+- Confirm shortening or ending an unavailability clears the Conflicting flag on bookings it no longer touches
+- Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -4659,39 +4828,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>B-08, C-65, T-66</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -4709,39 +4878,39 @@
 - Confirm suitability is advisory and does not itself block a booking request</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-21, B-08</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -4763,39 +4932,39 @@
 - View the status of each of my booking requests</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -4815,39 +4984,39 @@
 - Confirm the Coordinator is notified of either decision</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative and the hold is recorded against my event
@@ -4868,39 +5037,39 @@
 - Confirm only one active hold or confirmed booking exists per venue and period</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -4919,39 +5088,39 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -4968,39 +5137,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -5016,39 +5185,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -5064,39 +5233,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -5115,39 +5284,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -5160,39 +5329,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -5208,39 +5377,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -5259,39 +5428,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -5299,39 +5468,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -5339,39 +5508,39 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event confirmed
 Given the event has a confirmed venue booking and its full requested equipment reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details
@@ -5394,39 +5563,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a confirmed event to planning when an arrangement breaks so that its status reflects reality.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reverted with a recorded reason
 Given an event is Confirmed When I revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -5442,39 +5611,39 @@
 - Confirm the reversion is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -5492,39 +5661,39 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -5543,39 +5712,39 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -5596,39 +5765,39 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -5647,39 +5816,39 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -5698,39 +5867,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -5742,39 +5911,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -5790,39 +5959,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -5840,39 +6009,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -5891,39 +6060,39 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has a confirmed venue When its expected attendance is increased beyond that venue's capacity Then the venue booking is flagged for review and the Venue Staff are notified
@@ -5944,39 +6113,39 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an event to new dates so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Date change flags bookings
 Given an event has a confirmed venue and equipment When I change its date Then the existing bookings are flagged as requiring reconfirmation and are not moved silently
@@ -5984,39 +6153,39 @@
 Given Attendees have registered for the event When it is rescheduled Then all registered Attendees are notified of the new date and time</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -6035,52 +6204,12 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>E10 Changes, Rescheduling &amp; Cancellation</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>E10-S05</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Handle a venue lost from a confirmed event</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my confirmed events so that I can arrange an alternative before Attendees are affected.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Scenario 1 - Blocked venue flags the event
-Given my event has a confirmed venue When Venue Staff block that venue over the event's period Then I am notified and the event is flagged as at risk
-Scenario 2 - At-risk event offers a new search
-Given my event is flagged as at risk When I open it Then the reason and the affected arrangement are shown and I can begin a new venue search from that screen</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -6089,25 +6218,76 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
+          <t>E10 Changes, Rescheduling &amp; Cancellation</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Handle a venue lost from a confirmed event</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lost venue flags the event
+Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
+Scenario 2 - Flagged event offers a replacement search
+Given my event is flagged When I open it Then the reason category, the period and the affected booking are shown, the original venue, dates and requirements are preserved, and I can start a venue search (E06-S01) for the same event from that screen
+Scenario 3 - Replacement requested without losing the original
+Given I have found a replacement venue When I submit a booking request for it (E06-S03) Then the request is created for the same event alongside the Conflicting booking, and I may cancel the Conflicting booking explicitly once the replacement is Confirmed; nothing is cancelled for me
+Scenario 4 - Organiser and Attendees told on the actual change
+Given I confirm a replacement venue When the venue of a Confirmed event changes Then the Organiser and registered Attendees are notified of the new venue through the existing venue-change routing (E11-S01), and not earlier (assumes O-25)
+Checklist
+- Be notified when a venue I have booked is marked unavailable over my booking
+- See the reason, period and affected booking on the event, with the original event information intact
+- Start a venue search for the same event from the flagged event
+- Request a replacement venue while the Conflicting booking remains on the event until I cancel it
+- Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -6135,39 +6315,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -6175,39 +6355,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -6215,39 +6395,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -6255,39 +6435,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -6297,39 +6477,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -6337,39 +6517,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -6377,39 +6557,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -6418,39 +6598,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -6460,39 +6640,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -6500,39 +6680,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -6540,39 +6720,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -6592,15 +6772,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -1758,8 +1758,14 @@
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
 Scenario 2 - First request moves event to Planning
 Given the event has status Approved When the first booking request for any of its events is submitted Then the event status becomes Planning
-Scenario 3 - Second request for same event blocked
-Given the event already has a pending booking request When I submit another for the same event Then submission is blocked and the existing pending request is identified
+Scenario 3 - Several venue bookings for one event
+Given the event already has a Pending or Confirmed venue booking When I submit a request for another venue, or for the same venue over a different period, for the same event Then the request is created as Pending alongside the existing bookings, each booking keeps its own status, the event lists all of them, and withdrawing or changing one booking leaves the others untouched (C-67, T-68; replaces the earlier rule that blocked a second request, T-20 retired)
+#### Scenario 3a — Each booking carries its own purpose and headcount
+Given I am requesting one of several venues for an event When I submit the request Then I may record a purpose (for example "Main programme" or "Breakout A") and an expected headcount for that booking; suitability and capacity checks for that venue use the booking's headcount when present and the event's expected attendance otherwise (assumes O-27)
+#### Scenario 3b — Bookings may cover different windows inside the event
+Given an event runs 09:00 to 18:00 When I request a breakout room for 14:00 to 16:00 Then the request is accepted; a request whose period falls outside the event's start and end is refused (assumes O-29)
+#### Scenario 3c — One booking is the primary venue
+Given an event has more than one Confirmed venue booking When I view the event Then the first booking to be Confirmed is marked primary by default and I may mark a different Confirmed booking as primary; the primary venue is the one shown to Attendees (assumes O-30)
 Scenario 4 - Venue taken by another event blocked
 Given a venue is already Pending or Confirmed for another event over the same period When I submit a request for it Then submission is blocked and the conflict is explained
 Scenario 5 - Request conflicts through the buffer
@@ -1769,7 +1775,7 @@
 - Confirm the request is created as Pending and Venue Staff are notified
 - Confirm the venue calendar shows the period as Tentative
 - Confirm the event status moves from Approved to Planning on the first request
-- Be blocked from holding more than one pending request for the same event
+- Hold several venue bookings, Pending or Confirmed, for one event, each with an optional purpose and headcount, and mark one as primary (C-67; assumes O-27, O-30)
 - Be blocked from requesting a venue already Pending or Confirmed for another event in that period, counting that venue's setup and turnaround time (C-65)
 - View the status of each of my booking requests</t>
         </is>
@@ -1779,7 +1785,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66</t>
+          <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, O-27, O-29, O-30</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1933,6 +1939,8 @@
 Given another Venue Staff member approves a conflicting request moments before me When my approval is processed Then it fails and I am told the venue has just been taken
 Scenario 4 - Buffered windows are what must not overlap
 Given two pending requests on one venue whose advertised times do not overlap but whose buffered occupancy windows do When both are approved at the same moment Then at most one approval succeeds and the other fails safely, because the database-level conflict check operates on the buffered window (C-65, T-66, ADR-003)
+Scenario 5 - Conflicts are per venue, not per event
+Given one event has Pending requests on two different venues over the same period When both are approved Then both become Confirmed, because double-booking is detected per venue and an event may legitimately occupy several venues at once (C-67, T-68)
 Checklist
 - Be blocked from approving a request overlapping an existing confirmed booking
 - See which existing booking is causing the conflict
@@ -1947,7 +1955,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>C-46, T-22, C-65, T-66</t>
+          <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2349,9 +2357,9 @@
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event confirmed
-Given the event has a confirmed venue booking and its full requested equipment reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details
+Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, and its full requested equipment is reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details (C-67, T-68; assumes O-28)
 Scenario 2 - Missing venue blocks confirmation
-Given the event has no confirmed venue When I try to confirm Then confirmation is blocked and the outstanding items are listed
+Given the event has no Confirmed venue booking, or any of its venue bookings is still Pending or Conflicting When I try to confirm Then confirmation is blocked and each outstanding booking is listed by venue (assumes O-28)
 Scenario 3 - Partial equipment blocks confirmation
 Given the event has only a partial equipment reservation When I try to confirm Then confirmation is blocked and the outstanding quantity is shown
 Scenario 4 - None required does not block
@@ -2359,10 +2367,10 @@
 Scenario 5 - Outstanding support assignment blocks confirmation
 Given the event requested technical support and no staff are assigned When I try to confirm Then confirmation is blocked
 Scenario 6 - Organiser sees confirmed arrangements
-Given an event has been confirmed When the Event Organiser views it Then the confirmed venue, date, time and arrangements are shown
+Given an event has been confirmed When the Event Organiser views it Then every confirmed venue with its purpose and period, the date, time and arrangements are shown
 Checklist
 - Confirm an event that has a confirmed venue and full equipment reservation
-- Be blocked from confirming while the event lacks a venue
+- Be blocked from confirming while the event has no Confirmed venue booking or any booking still Pending or Conflicting, with each one listed (assumes O-28)
 - Be blocked from confirming while an equipment reservation is partial, with the shortfall shown
 - Confirm an event whose equipment requirement was recorded as 'none required'
 - Be blocked from confirming while a requested technical support assignment is outstanding
@@ -2374,7 +2382,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27</t>
+          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2521,6 +2529,8 @@
 Given a required registration field is empty When I submit Then registration is blocked and the missing fields are identified
 Scenario 4 - Unconfirmed event refused
 Given an event is not Confirmed When I attempt to register Then registration is refused
+Scenario 5 - One venue shown for a multi-venue event
+Given a Confirmed event has several Confirmed venue bookings When I view it to register Then the venue shown is the one its Coordinator marked primary, and the other venues are not listed as separate places to register (C-67; assumes O-30)
 Checklist
 - Register for a confirmed event
 - Provide name, email address and contact number as the required registration information
@@ -2535,7 +2545,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>C-35, T-48</t>
+          <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2945,7 +2955,7 @@
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
-Given an event has a confirmed venue When its expected attendance is increased beyond that venue's capacity Then the venue booking is flagged for review and the Venue Staff are notified
+Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
 Scenario 2 - Description-only edit flags nothing
 Given an event has a confirmed venue and equipment When only the event description is edited Then no arrangements are flagged
 Scenario 3 - Affected arrangements shown first
@@ -2953,7 +2963,7 @@
 Scenario 4 - Over-subscription warns only
 Given a venue change reduces the event's capacity below its registration count When the change is saved Then I am warned and shown the over-subscription, and no Attendee is automatically removed or waitlisted
 Scenario 5 - Date change flags venue and equipment
-Given the event's date or time changes When the change takes effect Then its venue booking and equipment reservations are flagged as requiring reconfirmation
+Given the event's date or time changes When the change takes effect Then every one of its venue bookings and its equipment reservations are flagged as requiring reconfirmation
 Checklist
 - Confirm attendance increases beyond venue capacity flag the booking for review
 - Confirm description-only edits flag nothing
@@ -2968,7 +2978,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>C-05, T-16, B-05, B-11</t>
+          <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -4747,8 +4757,14 @@
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
 Scenario 2 - First request moves event to Planning
 Given the event has status Approved When the first booking request for any of its events is submitted Then the event status becomes Planning
-Scenario 3 - Second request for same event blocked
-Given the event already has a pending booking request When I submit another for the same event Then submission is blocked and the existing pending request is identified
+Scenario 3 - Several venue bookings for one event
+Given the event already has a Pending or Confirmed venue booking When I submit a request for another venue, or for the same venue over a different period, for the same event Then the request is created as Pending alongside the existing bookings, each booking keeps its own status, the event lists all of them, and withdrawing or changing one booking leaves the others untouched (C-67, T-68; replaces the earlier rule that blocked a second request, T-20 retired)
+#### Scenario 3a — Each booking carries its own purpose and headcount
+Given I am requesting one of several venues for an event When I submit the request Then I may record a purpose (for example "Main programme" or "Breakout A") and an expected headcount for that booking; suitability and capacity checks for that venue use the booking's headcount when present and the event's expected attendance otherwise (assumes O-27)
+#### Scenario 3b — Bookings may cover different windows inside the event
+Given an event runs 09:00 to 18:00 When I request a breakout room for 14:00 to 16:00 Then the request is accepted; a request whose period falls outside the event's start and end is refused (assumes O-29)
+#### Scenario 3c — One booking is the primary venue
+Given an event has more than one Confirmed venue booking When I view the event Then the first booking to be Confirmed is marked primary by default and I may mark a different Confirmed booking as primary; the primary venue is the one shown to Attendees (assumes O-30)
 Scenario 4 - Venue taken by another event blocked
 Given a venue is already Pending or Confirmed for another event over the same period When I submit a request for it Then submission is blocked and the conflict is explained
 Scenario 5 - Request conflicts through the buffer
@@ -4758,7 +4774,7 @@
 - Confirm the request is created as Pending and Venue Staff are notified
 - Confirm the venue calendar shows the period as Tentative
 - Confirm the event status moves from Approved to Planning on the first request
-- Be blocked from holding more than one pending request for the same event
+- Hold several venue bookings, Pending or Confirmed, for one event, each with an optional purpose and headcount, and mark one as primary (C-67; assumes O-27, O-30)
 - Be blocked from requesting a venue already Pending or Confirmed for another event in that period, counting that venue's setup and turnaround time (C-65)
 - View the status of each of my booking requests</t>
         </is>
@@ -4768,7 +4784,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66</t>
+          <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, O-27, O-29, O-30</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -4910,6 +4926,8 @@
 Given another Venue Staff member approves a conflicting request moments before me When my approval is processed Then it fails and I am told the venue has just been taken
 Scenario 4 - Buffered windows are what must not overlap
 Given two pending requests on one venue whose advertised times do not overlap but whose buffered occupancy windows do When both are approved at the same moment Then at most one approval succeeds and the other fails safely, because the database-level conflict check operates on the buffered window (C-65, T-66, ADR-003)
+Scenario 5 - Conflicts are per venue, not per event
+Given one event has Pending requests on two different venues over the same period When both are approved Then both become Confirmed, because double-booking is detected per venue and an event may legitimately occupy several venues at once (C-67, T-68)
 Checklist
 - Be blocked from approving a request overlapping an existing confirmed booking
 - See which existing booking is causing the conflict
@@ -4924,7 +4942,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>C-46, T-22, C-65, T-66</t>
+          <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -5374,9 +5392,9 @@
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event confirmed
-Given the event has a confirmed venue booking and its full requested equipment reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details
+Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, and its full requested equipment is reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details (C-67, T-68; assumes O-28)
 Scenario 2 - Missing venue blocks confirmation
-Given the event has no confirmed venue When I try to confirm Then confirmation is blocked and the outstanding items are listed
+Given the event has no Confirmed venue booking, or any of its venue bookings is still Pending or Conflicting When I try to confirm Then confirmation is blocked and each outstanding booking is listed by venue (assumes O-28)
 Scenario 3 - Partial equipment blocks confirmation
 Given the event has only a partial equipment reservation When I try to confirm Then confirmation is blocked and the outstanding quantity is shown
 Scenario 4 - None required does not block
@@ -5384,10 +5402,10 @@
 Scenario 5 - Outstanding support assignment blocks confirmation
 Given the event requested technical support and no staff are assigned When I try to confirm Then confirmation is blocked
 Scenario 6 - Organiser sees confirmed arrangements
-Given an event has been confirmed When the Event Organiser views it Then the confirmed venue, date, time and arrangements are shown
+Given an event has been confirmed When the Event Organiser views it Then every confirmed venue with its purpose and period, the date, time and arrangements are shown
 Checklist
 - Confirm an event that has a confirmed venue and full equipment reservation
-- Be blocked from confirming while the event lacks a venue
+- Be blocked from confirming while the event has no Confirmed venue booking or any booking still Pending or Conflicting, with each one listed (assumes O-28)
 - Be blocked from confirming while an equipment reservation is partial, with the shortfall shown
 - Confirm an event whose equipment requirement was recorded as 'none required'
 - Be blocked from confirming while a requested technical support assignment is outstanding
@@ -5399,7 +5417,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27</t>
+          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -5534,6 +5552,8 @@
 Given a required registration field is empty When I submit Then registration is blocked and the missing fields are identified
 Scenario 4 - Unconfirmed event refused
 Given an event is not Confirmed When I attempt to register Then registration is refused
+Scenario 5 - One venue shown for a multi-venue event
+Given a Confirmed event has several Confirmed venue bookings When I view it to register Then the venue shown is the one its Coordinator marked primary, and the other venues are not listed as separate places to register (C-67; assumes O-30)
 Checklist
 - Register for a confirmed event
 - Provide name, email address and contact number as the required registration information
@@ -5548,7 +5568,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>C-35, T-48</t>
+          <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -5926,7 +5946,7 @@
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
-Given an event has a confirmed venue When its expected attendance is increased beyond that venue's capacity Then the venue booking is flagged for review and the Venue Staff are notified
+Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
 Scenario 2 - Description-only edit flags nothing
 Given an event has a confirmed venue and equipment When only the event description is edited Then no arrangements are flagged
 Scenario 3 - Affected arrangements shown first
@@ -5934,7 +5954,7 @@
 Scenario 4 - Over-subscription warns only
 Given a venue change reduces the event's capacity below its registration count When the change is saved Then I am warned and shown the over-subscription, and no Attendee is automatically removed or waitlisted
 Scenario 5 - Date change flags venue and equipment
-Given the event's date or time changes When the change takes effect Then its venue booking and equipment reservations are flagged as requiring reconfirmation
+Given the event's date or time changes When the change takes effect Then every one of its venue bookings and its equipment reservations are flagged as requiring reconfirmation
 Checklist
 - Confirm attendance increases beyond venue capacity flag the booking for review
 - Confirm description-only edits flag nothing
@@ -5949,7 +5969,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>C-05, T-16, B-05, B-11</t>
+          <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -1869,28 +1869,41 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised.</t>
+          <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
+The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
-Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative and the hold is recorded against my event
+Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
 Scenario 2 - Slot already held or booked
 Given a venue already has a tentative hold or a confirmed booking for the period When I attempt to hold it for another event Then the hold is refused and the existing hold or booking is identified
 Scenario 3 - Hold becomes a booking request
-Given I hold a venue tentatively When I submit a booking request for that venue Then the hold becomes a pending booking request for the same period
+Given I hold a venue tentatively When I submit a booking request for that venue Then the hold becomes a pending booking request for the same period and the expiry no longer applies, because submitting the request is the action that completes the hold (assumes O-32)
 Scenario 4 - Hold released
 Given I hold a venue tentatively and no longer need it When I release the hold Then the period returns to Free on the calendar
 Scenario 5 - Hold occupies the buffered window
 Given a venue has a setup time of 30 minutes and a turnaround time of 45 minutes When I hold it tentatively for 10:00 to 12:00 Then the hold occupies 09:30 to 12:45, the calendar shows that window as Tentative, and another hold or booking request overlapping any part of it is refused (C-65, T-66)
+Scenario 6 - Hold expires and frees the venue
+Given my hold's expiry date and time has passed and I have not submitted a booking request for it When the expiry job next runs Then the hold's status becomes Expired, the period returns to Free on the calendar, the venue can be held or requested by any event, and an Expired hold is never counted as a Confirmed or Pending booking anywhere, including the E08-S03 confirmation gate (C-68, T-69)
+Scenario 7 - Coordinator told before and at expiry
+Given my hold will expire in 24 hours When that moment passes Then I receive an in-app and email reminder naming the venue, the event and the expiry time; and Given the hold expires When the expiry job runs Then I receive an in-app and email notice that it has expired and the venue is free (assumes O-33)
+Scenario 8 - Venue Staff may extend a hold
+Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, the extension is recorded in the activity log with who made it, and the reminder is rescheduled; an expired hold cannot be extended and must be placed again (assumes O-34)
+Scenario 9 - Expiry exactly at the boundary
+Given a hold expires at 10:00:00 When the expiry job runs at 09:59:59 Then the hold is still Tentative, and when it runs at 10:00:00 or later Then the hold is Expired
 Checklist
 - Place a tentative hold on a venue that is free for the period
 - See the period shown as Tentative on the venue calendar
 - Be refused when the slot already has a tentative hold or a confirmed booking for another event
 - Convert a tentative hold into a booking request
 - Release a tentative hold, returning the period to Free
-- Confirm only one active hold or confirmed booking exists per venue and period</t>
+- Confirm only one active hold or confirmed booking exists per venue and period
+- See the expiry date and time on every hold, defaulting to 48 hours after creation (assumes O-31)
+- Confirm an expired hold frees the venue and is never treated as a booking
+- Receive a reminder before and a notice at expiry (assumes O-33)
+- Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -1898,7 +1911,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66</t>
+          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -3097,7 +3110,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64</t>
+          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -4860,28 +4873,41 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised.</t>
+          <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
+The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
-Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative and the hold is recorded against my event
+Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
 Scenario 2 - Slot already held or booked
 Given a venue already has a tentative hold or a confirmed booking for the period When I attempt to hold it for another event Then the hold is refused and the existing hold or booking is identified
 Scenario 3 - Hold becomes a booking request
-Given I hold a venue tentatively When I submit a booking request for that venue Then the hold becomes a pending booking request for the same period
+Given I hold a venue tentatively When I submit a booking request for that venue Then the hold becomes a pending booking request for the same period and the expiry no longer applies, because submitting the request is the action that completes the hold (assumes O-32)
 Scenario 4 - Hold released
 Given I hold a venue tentatively and no longer need it When I release the hold Then the period returns to Free on the calendar
 Scenario 5 - Hold occupies the buffered window
 Given a venue has a setup time of 30 minutes and a turnaround time of 45 minutes When I hold it tentatively for 10:00 to 12:00 Then the hold occupies 09:30 to 12:45, the calendar shows that window as Tentative, and another hold or booking request overlapping any part of it is refused (C-65, T-66)
+Scenario 6 - Hold expires and frees the venue
+Given my hold's expiry date and time has passed and I have not submitted a booking request for it When the expiry job next runs Then the hold's status becomes Expired, the period returns to Free on the calendar, the venue can be held or requested by any event, and an Expired hold is never counted as a Confirmed or Pending booking anywhere, including the E08-S03 confirmation gate (C-68, T-69)
+Scenario 7 - Coordinator told before and at expiry
+Given my hold will expire in 24 hours When that moment passes Then I receive an in-app and email reminder naming the venue, the event and the expiry time; and Given the hold expires When the expiry job runs Then I receive an in-app and email notice that it has expired and the venue is free (assumes O-33)
+Scenario 8 - Venue Staff may extend a hold
+Given a hold has not yet expired When Venue Staff set a later expiry date and time Then the new expiry applies, the extension is recorded in the activity log with who made it, and the reminder is rescheduled; an expired hold cannot be extended and must be placed again (assumes O-34)
+Scenario 9 - Expiry exactly at the boundary
+Given a hold expires at 10:00:00 When the expiry job runs at 09:59:59 Then the hold is still Tentative, and when it runs at 10:00:00 or later Then the hold is Expired
 Checklist
 - Place a tentative hold on a venue that is free for the period
 - See the period shown as Tentative on the venue calendar
 - Be refused when the slot already has a tentative hold or a confirmed booking for another event
 - Convert a tentative hold into a booking request
 - Release a tentative hold, returning the period to Free
-- Confirm only one active hold or confirmed booking exists per venue and period</t>
+- Confirm only one active hold or confirmed booking exists per venue and period
+- See the expiry date and time on every hold, defaulting to 48 hours after creation (assumes O-31)
+- Confirm an expired hold frees the venue and is never treated as a booking
+- Receive a reminder before and a notice at expiry (assumes O-33)
+- Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
@@ -4889,7 +4915,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66</t>
+          <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -6160,7 +6186,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64</t>
+          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -837,30 +837,137 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>E01 Access &amp; Identity</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>E01-S12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Manage only the events assigned to me as an Event Coordinator</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator, I want my event list and event actions to cover only the events assigned to me so that I manage my own work and cannot act on a colleague's event by mistake.
+New story from the Week 7 Customer Changes (C-69). E01-S02 (Organiser isolation) is Done and stays Done; this story extends the same discipline to a second role rather than editing it (T-74). Venue availability (C-40, E05-S03) is unaffected: Coordinators still see every venue's calendar states, with other events' details withheld as E05-S03 Scenario 2 already requires. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Own assigned events only
+Given events are assigned to me and to other Coordinators When I open my event list Then only the events assigned to me are shown
+Scenario 2 - Direct access to a colleague's event refused
+Given an event is assigned to another Coordinator When I navigate directly to its identifier or attempt any action on it Then access is refused, nothing about the event is revealed, and the attempt is recorded in the activity log
+Scenario 3 - Unassigned requests not visible to Coordinators
+Given requests are in the unassigned queue When I open my event list Then they are not shown, because the queue belongs to the Lead (assumes O-38)
+Scenario 4 - Venue calendars still visible
+Given other Coordinators' events hold venue bookings When I open a venue availability calendar Then the Free, Tentative, Confirmed and Blocked states are shown for every period while the other events' details are withheld, exactly as in E05-S03 Scenario 2
+Scenario 5 - Organiser isolation unchanged
+Given an Event Organiser for Client A is signed in When they open their event list Then E01-S02 Scenarios 1 to 3 hold unchanged
+Checklist
+- See only the events assigned to me in my event list
+- Be refused, with the attempt logged, when opening or acting on another Coordinator's event
+- Not see the unassigned queue
+- Still see every venue's availability states with other events' details withheld
+- Confirm the Organiser's client isolation (E01-S02) is unchanged</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>C-69, C-40, T-70, T-73, T-74, O-38</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>E01 Access &amp; Identity</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>E01-S13</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Sign in as an Event Coordinator Lead or Safety Officer</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead or a Safety Officer, I want to sign in and land on the workspace for my role so that I can start on the queue of work that belongs to me.
+New story from the Week 7 Customer Changes (C-69, C-70) adding the sixth and seventh roles (T-72). E01-S01 (log in) is Done and stays Done; the two new roles' landing pages are this story rather than an edit to it (T-74). Accounts are pre-seeded like every other internal role (C-57). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lead lands on the unassigned queue
+Given I am a pre-seeded Event Coordinator Lead When I sign in with valid credentials Then I am taken to the unassigned queue (E03-S08) with the oversight view (E03-S10) one step away, and the navigation shows only the Lead's pages
+Scenario 2 - Safety Officer lands on the safety review queue
+Given I am a pre-seeded Safety Officer When I sign in with valid credentials Then I am taken to the list of events awaiting Operational Safety Check (E08-S07), and the navigation shows only the Safety Officer's pages
+Scenario 3 - One role per account
+Given a Lead or Safety Officer account exists When its role is inspected Then it holds exactly that one role and no Coordinator permissions, consistent with ADR-012 (assumes O-44)
+Scenario 4 - Existing roles' sign-in unchanged
+Given an Organiser, Coordinator, Venue Staff member, Technical Support Staff member and Attendee each sign in When they land Then each reaches the same dashboard as before this story, so E01-S01 Scenario 1 holds for all five existing roles
+Checklist
+- Sign in as a Lead and land on the unassigned queue with the Lead's navigation
+- Sign in as a Safety Officer and land on the safety review queue with the Safety Officer's navigation
+- Confirm each new-role account holds exactly one role
+- Confirm the five existing roles still land where they did</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>C-69, C-70, C-57, T-72, T-73, T-74, O-44</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>E02-S01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Submit an event request</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to submit an event request so that ConnectSphere can begin planning my event.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Complete request submitted
 Given I am signed in as an Event Organiser and every mandatory field is complete When I submit the request Then its status becomes Submitted and I receive confirmation
@@ -878,47 +985,47 @@
 - See the status change to Submitted and receive confirmation</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>C-36, T-11, T-12</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Aaron</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>E02-S02</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Save a draft event request</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to save an incomplete event request as a draft so that I can gather the missing information and complete it later.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Draft saved and hidden from Coordinators
 Given I have partially completed a request When I save it as a draft Then it is stored with status Draft and is not visible to Event Coordinators
@@ -937,47 +1044,47 @@
 - Confirm that Event Coordinators cannot see my drafts</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Aaron</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>E02-S03</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Match accessibility requirements to venue features</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the accessibility requirements for my event so that ConnectSphere only offers venues that can meet them.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Predefined requirements stored
 Given I am creating an event request When I select one or more accessibility requirements from the predefined list Then they are stored with the request and shown to the assigned Event Coordinator
@@ -992,51 +1099,52 @@
 - Confirm that predefined requirements filter the venue search results</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>T-13, T-45, B-06</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Aaron</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>E03-S01</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Assign an Event Coordinator to a request</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>As an Event Organiser, I want my submitted request to be assigned an Event Coordinator automatically so that my event has one clear internal owner from the outset.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Scenario 1 - Exactly one Coordinator assigned
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want my submitted request to be assigned an Event Coordinator automatically so that my event has one clear internal owner from the outset.
+Done in Sprint 2 (#141, #147) and kept Done (T-74). The Week 7 Customer Changes (C-69) end automatic assignment: Scenarios 1 and 2 and the first two checklist items are superseded by E03-S08, which puts new requests in an unassigned queue worked by the Event Coordinator Lead. They stay here as the record of what was delivered. Scenarios 3 to 6 remain in force; E03-S09 adds the Lead as a second actor who may reassign directly.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - [Superseded by E03-S08 (C-69)] Exactly one Coordinator assigned
 Given a request is submitted When submission completes Then the system assigns exactly one Event Coordinator, the status becomes Under Review, and that Coordinator is notified
-Scenario 2 - Fewest active events wins
+Scenario 2 - [Superseded by E03-S08 (C-69)] Fewest active events wins
 Given several Event Coordinators are available When the system assigns one Then it selects the Coordinator with the fewest active events
 Scenario 3 - Reassignment requested
 Given I am the assigned Coordinator and a reassignment has been agreed offline When I request reassignment to a named colleague Then the request is recorded, that colleague is notified, and I remain assigned until they accept
@@ -1047,8 +1155,8 @@
 Scenario 6 - Unassigned Coordinator refused
 Given I am not the assigned Coordinator When I attempt to reassign the event Then the action is refused
 Checklist
-- Confirm that exactly one Event Coordinator is assigned on submission
-- Confirm the assigned Coordinator is the one with the fewest active events
+- Confirm that exactly one Event Coordinator is assigned on submission (superseded by E03-S08, C-69)
+- Confirm the assigned Coordinator is the one with the fewest active events (superseded by E03-S08, C-69; the count is now shown to the Lead as advice)
 - Confirm the status moves from Submitted to Under Review
 - Request reassignment to a named colleague as the assigned Coordinator
 - Confirm the original Coordinator stays assigned until the colleague accepts
@@ -1057,43 +1165,43 @@
 - Be refused when attempting to reassign an event assigned to someone else</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>C-12, C-41, C-55, C-56, T-14, T-15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>C-12, C-41, C-55, C-56, T-14, T-15, C-69, T-70, T-74</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>E03-S02</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Request clarification from the Event Organiser</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a request to the Event Organiser with specific questions so that unclear requirements are corrected before planning begins.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Questions sent, status changes
 Given I am reviewing a request with status Under Review When I record my questions and send them Then the status becomes Awaiting Clarification and the Event Organiser is notified with the questions
@@ -1109,43 +1217,43 @@
 - Filter my events by clarification status</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>C-10, B-02</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>E03-S03</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Decide on an event request</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to approve or reject a request and record my reasoning so that the Event Organiser receives a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Approved to planning
 Given a request has status Under Review and the required information is complete When I approve it Then the status becomes Approved and the Event Organiser is notified
@@ -1168,43 +1276,43 @@
 - Confirm a rejected request is read-only</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>C-09, T-39, T-41, T-43, O-06</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>E03-S05</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Track the status of my event</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to see the current status of my event so that I know what stage planning has reached without contacting my Coordinator.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Current status in plain language
 Given my event is at any stage When I open it Then the current status and the date it was reached are shown in plain language
@@ -1217,43 +1325,43 @@
 - See the full status history for my event, drawn from the activity log (E14-S02)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>E03-S06</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Discuss an event through comments</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to post comments and questions on my event record so that planning conversations with my Coordinator are kept with the event rather than scattered across email.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Comment posted and Coordinator notified
 Given I have access to an event When I post a comment Then it appears on the event with my name and the time it was posted, and the assigned Coordinator is notified
@@ -1269,43 +1377,43 @@
 - Be refused when posting on an event I cannot access</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>C-15, C-47, B-02</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>E03-S07</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>View and update event information</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view and update event information while planning is underway so that the record stays accurate as details are settled.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Organiser edits before approval
 Given an event has not yet been approved When the Event Organiser edits any field Then the change is saved directly against the event
@@ -1326,43 +1434,206 @@
 - Confirm every post-approval edit is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>C-52, T-16</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>E03-S08</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Assign a queued request to an Event Coordinator as the Lead</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead, I want newly submitted event requests to enter an unassigned queue that I work through, assigning each to a suitable Event Coordinator, so that incoming work is distributed deliberately rather than automatically.
+New story from the Week 7 Customer Changes (C-69). It replaces the automatic assignment delivered by E03-S01 Scenarios 1 and 2, which stay recorded there as superseded (T-74). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Submission enters the unassigned queue
+Given an Event Organiser submits a request When submission completes Then no Event Coordinator is assigned, the event's status stays Submitted, the request appears in the unassigned queue, and the Event Coordinator Lead is notified (replaces E03-S01 Scenarios 1 and 2)
+Scenario 2 - Queue shows basic event information, oldest first
+Given requests are in the unassigned queue When I open it Then each shows the event name, the Organiser's client organisation, preferred dates, expected attendance and the time submitted, oldest first, and the queue is visible to Event Coordinator Leads only (assumes O-38)
+Scenario 3 - Lead assigns a Coordinator
+Given a request is in the queue When I choose an Event Coordinator and assign Then exactly one Coordinator is assigned, the status becomes Under Review, the Coordinator and the Organiser are notified, the request leaves the queue, and the activity log records who assigned it and when
+Scenario 4 - Workload shown while choosing
+Given I am choosing a Coordinator When the list of Coordinators is shown Then each shows their count of active events, so the fewest-active-events rule the system used to apply (T-14) is available as advice without being enforced
+Scenario 5 - Only a Lead may assign from the queue
+Given I am an Event Coordinator or any role other than Event Coordinator Lead When I attempt to assign a queued request Then the action is refused and the refusal is recorded in the activity log
+Scenario 6 - Status transition and Organiser view unchanged
+Given a request has been assigned from the queue When the Organiser tracks the event (E03-S05) Then the status history shows Submitted followed by Under Review exactly as it did under automatic assignment, so E03-S01's delivered transition still holds
+Checklist
+- Confirm a newly submitted request has no Coordinator, stays Submitted and appears in the unassigned queue
+- Confirm the Lead is notified of each new queued request
+- See each queued request's basic information, oldest first, as a Lead only
+- Assign exactly one Coordinator from the queue, moving the event to Under Review with the Coordinator and Organiser notified and the action logged
+- See each Coordinator's active-event count while choosing
+- Be refused as a non-Lead when attempting to assign from the queue
+- Confirm the Submitted to Under Review transition recorded by E03-S01 is unchanged</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>C-69, T-70, T-72, T-73, T-74, O-35, O-38</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>E03-S09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Reassign an event as the Lead</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead, I want to reassign an event to a different Event Coordinator where necessary so that workload, absences and conflicts can be managed without waiting on the current Coordinator.
+New story from the Week 7 Customer Changes (C-69). The Coordinator-initiated reassignment with acceptance delivered by E03-S01 Scenarios 3 to 6 stays in force (T-15 amended, not replaced). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lead reassignment takes effect immediately
+Given an event is assigned to a Coordinator When I, as the Lead, reassign it to another Coordinator Then the change takes effect at once without an acceptance step, the outgoing and incoming Coordinators and the Organiser are notified, and the activity log records who reassigned it and when (assumes O-36)
+Scenario 2 - Coordinator-initiated reassignment unchanged
+Given I am the assigned Coordinator and a reassignment has been agreed offline When I request reassignment to a named colleague Then E03-S01 Scenarios 3, 4 and 5 apply unchanged: I remain assigned until the colleague accepts, and a decline leaves me assigned
+Scenario 3 - Coordinator may ask the Lead to reassign
+Given I am the assigned Coordinator When I request reassignment without naming a colleague Then the request appears to the Lead with my reason, I remain assigned until the Lead acts, and the Lead may reassign (Scenario 1) or decline, which notifies me (assumes O-37)
+Scenario 4 - Only the assigned Coordinator or a Lead may reassign
+Given I am a Coordinator not assigned to the event When I attempt to reassign it Then the action is refused, exactly as in E03-S01 Scenario 6
+Checklist
+- Reassign an event directly as the Lead, with both Coordinators and the Organiser notified and the change logged
+- Confirm Coordinator-to-Coordinator reassignment still requires the colleague's acceptance
+- Ask the Lead to reassign my event without naming a colleague, and be told the outcome
+- Be refused when attempting to reassign an event I am not assigned to and am not the Lead for</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>C-69, C-56, T-15, T-70, T-73, T-74, O-36, O-37</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>E03-S10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Oversee coordinator assignments and active events as the Lead</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead, I want to view every coordinator assignment and every active event under my supervision so that I can see workload across the team and step in where needed.
+New story from the Week 7 Customer Changes (C-69). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Every active event and its Coordinator listed
+Given events exist in every status When I open the oversight view Then every event whose status is Submitted, Under Review, Awaiting Clarification, Approved, Planning, Safety Review or Confirmed is listed with its assigned Coordinator or "Unassigned", and I can filter by Coordinator and by status
+Scenario 2 - Workload per Coordinator
+Given Coordinators have events assigned When I open the workload summary Then each Coordinator is shown with their count of active events and the list of those events
+Scenario 3 - One Lead sees everything
+Given there is one Event Coordinator Lead in Release 1 When I open the oversight view Then every assignment and active event is included regardless of which Coordinator holds it (assumes O-35)
+Scenario 4 - Coordinators cannot open the oversight view
+Given I am an Event Coordinator When I navigate to the oversight view Then access is refused and the attempt is recorded in the activity log
+Checklist
+- See every active event with its assigned Coordinator or Unassigned, filterable by Coordinator and status
+- See each Coordinator's active-event count and events
+- Confirm the view covers every assignment, not a subset
+- Be refused as a Coordinator</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>C-69, T-70, T-73, O-35</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -1381,47 +1652,47 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -1437,47 +1708,47 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -1494,43 +1765,43 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -1546,44 +1817,44 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03 because that story is Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -1605,43 +1876,43 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -1662,43 +1933,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>B-08, C-65, T-66</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -1716,43 +1987,43 @@
 - Confirm suitability is advisory and does not itself block a booking request</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-21, B-08</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -1780,43 +2051,43 @@
 - View the status of each of my booking requests</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, O-27, O-29, O-30</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -1836,44 +2107,44 @@
 - Confirm the Coordinator is notified of either decision</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -1906,43 +2177,43 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -1963,43 +2234,43 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -2016,43 +2287,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2068,43 +2339,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2120,43 +2391,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2175,43 +2446,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2224,43 +2495,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2276,43 +2547,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2331,43 +2602,43 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event confirmed
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, and its full requested equipment is reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details (C-67, T-68; assumes O-28)
@@ -2390,43 +2661,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a confirmed event to planning when an arrangement breaks so that its status reflects reality.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reverted with a recorded reason
 Given an event is Confirmed When I revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -2442,43 +2713,43 @@
 - Confirm the reversion is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -2496,43 +2767,43 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -2553,43 +2824,43 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -2610,43 +2881,43 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -2665,43 +2936,43 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -2720,43 +2991,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -2768,43 +3039,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -2820,43 +3091,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -2874,43 +3145,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -2929,43 +3200,43 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
@@ -2986,43 +3257,43 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -3041,43 +3312,43 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3105,43 +3376,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -3161,15 +3432,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -3186,7 +3457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3719,25 +3990,124 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>E01 Access &amp; Identity</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>E01-S12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Manage only the events assigned to me as an Event Coordinator</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator, I want my event list and event actions to cover only the events assigned to me so that I manage my own work and cannot act on a colleague's event by mistake.
+New story from the Week 7 Customer Changes (C-69). E01-S02 (Organiser isolation) is Done and stays Done; this story extends the same discipline to a second role rather than editing it (T-74). Venue availability (C-40, E05-S03) is unaffected: Coordinators still see every venue's calendar states, with other events' details withheld as E05-S03 Scenario 2 already requires. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Own assigned events only
+Given events are assigned to me and to other Coordinators When I open my event list Then only the events assigned to me are shown
+Scenario 2 - Direct access to a colleague's event refused
+Given an event is assigned to another Coordinator When I navigate directly to its identifier or attempt any action on it Then access is refused, nothing about the event is revealed, and the attempt is recorded in the activity log
+Scenario 3 - Unassigned requests not visible to Coordinators
+Given requests are in the unassigned queue When I open my event list Then they are not shown, because the queue belongs to the Lead (assumes O-38)
+Scenario 4 - Venue calendars still visible
+Given other Coordinators' events hold venue bookings When I open a venue availability calendar Then the Free, Tentative, Confirmed and Blocked states are shown for every period while the other events' details are withheld, exactly as in E05-S03 Scenario 2
+Scenario 5 - Organiser isolation unchanged
+Given an Event Organiser for Client A is signed in When they open their event list Then E01-S02 Scenarios 1 to 3 hold unchanged
+Checklist
+- See only the events assigned to me in my event list
+- Be refused, with the attempt logged, when opening or acting on another Coordinator's event
+- Not see the unassigned queue
+- Still see every venue's availability states with other events' details withheld
+- Confirm the Organiser's client isolation (E01-S02) is unchanged</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>C-69, C-40, T-70, T-73, T-74, O-38</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>E01 Access &amp; Identity</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>E01-S13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Sign in as an Event Coordinator Lead or Safety Officer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead or a Safety Officer, I want to sign in and land on the workspace for my role so that I can start on the queue of work that belongs to me.
+New story from the Week 7 Customer Changes (C-69, C-70) adding the sixth and seventh roles (T-72). E01-S01 (log in) is Done and stays Done; the two new roles' landing pages are this story rather than an edit to it (T-74). Accounts are pre-seeded like every other internal role (C-57). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lead lands on the unassigned queue
+Given I am a pre-seeded Event Coordinator Lead When I sign in with valid credentials Then I am taken to the unassigned queue (E03-S08) with the oversight view (E03-S10) one step away, and the navigation shows only the Lead's pages
+Scenario 2 - Safety Officer lands on the safety review queue
+Given I am a pre-seeded Safety Officer When I sign in with valid credentials Then I am taken to the list of events awaiting Operational Safety Check (E08-S07), and the navigation shows only the Safety Officer's pages
+Scenario 3 - One role per account
+Given a Lead or Safety Officer account exists When its role is inspected Then it holds exactly that one role and no Coordinator permissions, consistent with ADR-012 (assumes O-44)
+Scenario 4 - Existing roles' sign-in unchanged
+Given an Organiser, Coordinator, Venue Staff member, Technical Support Staff member and Attendee each sign in When they land Then each reaches the same dashboard as before this story, so E01-S01 Scenario 1 holds for all five existing roles
+Checklist
+- Sign in as a Lead and land on the unassigned queue with the Lead's navigation
+- Sign in as a Safety Officer and land on the safety review queue with the Safety Officer's navigation
+- Confirm each new-role account holds exactly one role
+- Confirm the five existing roles still land where they did</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>C-69, C-70, C-57, T-72, T-73, T-74, O-44</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>E02-S01</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Submit an event request</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to submit an event request so that ConnectSphere can begin planning my event.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Complete request submitted
 Given I am signed in as an Event Organiser and every mandatory field is complete When I submit the request Then its status becomes Submitted and I receive confirmation
@@ -3755,39 +4125,39 @@
 - See the status change to Submitted and receive confirmation</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>C-36, T-11, T-12</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>E02-S02</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Save a draft event request</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to save an incomplete event request as a draft so that I can gather the missing information and complete it later.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Draft saved and hidden from Coordinators
 Given I have partially completed a request When I save it as a draft Then it is stored with status Draft and is not visible to Event Coordinators
@@ -3806,39 +4176,39 @@
 - Confirm that Event Coordinators cannot see my drafts</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>E02-S03</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Match accessibility requirements to venue features</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the accessibility requirements for my event so that ConnectSphere only offers venues that can meet them.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Predefined requirements stored
 Given I am creating an event request When I select one or more accessibility requirements from the predefined list Then they are stored with the request and shown to the assigned Event Coordinator
@@ -3853,39 +4223,39 @@
 - Confirm that predefined requirements filter the venue search results</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>T-13, T-45, B-06</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>E02-S04</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Classify an event by category</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to assign a category to an event from a predefined list so that events are classified to support filtering and reporting.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Category saved
 Given I am creating or editing an event When I select a category from ConnectSphere's list Then it is saved against the event
@@ -3893,39 +4263,39 @@
 Given ConnectSphere adds a new category When I next create an event Then the new category is available for selection</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>C-32, O-13</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>E02-S05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Reuse a previous event's details</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to create a new request by copying a previous event so that I do not re-enter the same information for a recurring event.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Previous event copied
 Given I have a previous event When I choose to copy it Then a new draft is created with the requirements copied and the dates left blank
@@ -3933,39 +4303,39 @@
 Given the copied event referenced a venue or equipment item that no longer exists When the draft is created Then that requirement is flagged for review rather than copied silently</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>E02 Event Request &amp; Submission</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>E02-S06</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Attach supporting documents</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to attach documents such as floor plans and programmes to my event so that ConnectSphere has the materials it needs.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted file attached
 Given I am viewing an event I own When I upload a PDF, PNG or JPEG of 300MB or less Then it is attached to the event and visible to the assigned internal users
@@ -3980,43 +4350,44 @@
 - Delete an attachment, with the deletion recorded in the activity log</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>C-31, T-40, O-08</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>E03-S01</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Assign an Event Coordinator to a request</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>As an Event Organiser, I want my submitted request to be assigned an Event Coordinator automatically so that my event has one clear internal owner from the outset.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Scenario 1 - Exactly one Coordinator assigned
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want my submitted request to be assigned an Event Coordinator automatically so that my event has one clear internal owner from the outset.
+Done in Sprint 2 (#141, #147) and kept Done (T-74). The Week 7 Customer Changes (C-69) end automatic assignment: Scenarios 1 and 2 and the first two checklist items are superseded by E03-S08, which puts new requests in an unassigned queue worked by the Event Coordinator Lead. They stay here as the record of what was delivered. Scenarios 3 to 6 remain in force; E03-S09 adds the Lead as a second actor who may reassign directly.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - [Superseded by E03-S08 (C-69)] Exactly one Coordinator assigned
 Given a request is submitted When submission completes Then the system assigns exactly one Event Coordinator, the status becomes Under Review, and that Coordinator is notified
-Scenario 2 - Fewest active events wins
+Scenario 2 - [Superseded by E03-S08 (C-69)] Fewest active events wins
 Given several Event Coordinators are available When the system assigns one Then it selects the Coordinator with the fewest active events
 Scenario 3 - Reassignment requested
 Given I am the assigned Coordinator and a reassignment has been agreed offline When I request reassignment to a named colleague Then the request is recorded, that colleague is notified, and I remain assigned until they accept
@@ -4027,8 +4398,8 @@
 Scenario 6 - Unassigned Coordinator refused
 Given I am not the assigned Coordinator When I attempt to reassign the event Then the action is refused
 Checklist
-- Confirm that exactly one Event Coordinator is assigned on submission
-- Confirm the assigned Coordinator is the one with the fewest active events
+- Confirm that exactly one Event Coordinator is assigned on submission (superseded by E03-S08, C-69)
+- Confirm the assigned Coordinator is the one with the fewest active events (superseded by E03-S08, C-69; the count is now shown to the Lead as advice)
 - Confirm the status moves from Submitted to Under Review
 - Request reassignment to a named colleague as the assigned Coordinator
 - Confirm the original Coordinator stays assigned until the colleague accepts
@@ -4037,39 +4408,39 @@
 - Be refused when attempting to reassign an event assigned to someone else</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>C-12, C-41, C-55, C-56, T-14, T-15</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>C-12, C-41, C-55, C-56, T-14, T-15, C-69, T-70, T-74</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>E03-S02</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Request clarification from the Event Organiser</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a request to the Event Organiser with specific questions so that unclear requirements are corrected before planning begins.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Questions sent, status changes
 Given I am reviewing a request with status Under Review When I record my questions and send them Then the status becomes Awaiting Clarification and the Event Organiser is notified with the questions
@@ -4085,39 +4456,39 @@
 - Filter my events by clarification status</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>C-10, B-02</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>E03-S03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Decide on an event request</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to approve or reject a request and record my reasoning so that the Event Organiser receives a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Approved to planning
 Given a request has status Under Review and the required information is complete When I approve it Then the status becomes Approved and the Event Organiser is notified
@@ -4140,39 +4511,39 @@
 - Confirm a rejected request is read-only</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>C-09, T-39, T-41, T-43, O-06</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>E03-S05</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Track the status of my event</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to see the current status of my event so that I know what stage planning has reached without contacting my Coordinator.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Current status in plain language
 Given my event is at any stage When I open it Then the current status and the date it was reached are shown in plain language
@@ -4185,39 +4556,39 @@
 - See the full status history for my event, drawn from the activity log (E14-S02)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>E03-S06</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Discuss an event through comments</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to post comments and questions on my event record so that planning conversations with my Coordinator are kept with the event rather than scattered across email.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Comment posted and Coordinator notified
 Given I have access to an event When I post a comment Then it appears on the event with my name and the time it was posted, and the assigned Coordinator is notified
@@ -4233,39 +4604,39 @@
 - Be refused when posting on an event I cannot access</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>C-15, C-47, B-02</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>E03 Review, Coordination &amp; Status</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>E03-S07</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>View and update event information</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view and update event information while planning is underway so that the record stays accurate as details are settled.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Organiser edits before approval
 Given an event has not yet been approved When the Event Organiser edits any field Then the change is saved directly against the event
@@ -4286,39 +4657,190 @@
 - Confirm every post-approval edit is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>C-52, T-16</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>E03-S08</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Assign a queued request to an Event Coordinator as the Lead</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead, I want newly submitted event requests to enter an unassigned queue that I work through, assigning each to a suitable Event Coordinator, so that incoming work is distributed deliberately rather than automatically.
+New story from the Week 7 Customer Changes (C-69). It replaces the automatic assignment delivered by E03-S01 Scenarios 1 and 2, which stay recorded there as superseded (T-74). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Submission enters the unassigned queue
+Given an Event Organiser submits a request When submission completes Then no Event Coordinator is assigned, the event's status stays Submitted, the request appears in the unassigned queue, and the Event Coordinator Lead is notified (replaces E03-S01 Scenarios 1 and 2)
+Scenario 2 - Queue shows basic event information, oldest first
+Given requests are in the unassigned queue When I open it Then each shows the event name, the Organiser's client organisation, preferred dates, expected attendance and the time submitted, oldest first, and the queue is visible to Event Coordinator Leads only (assumes O-38)
+Scenario 3 - Lead assigns a Coordinator
+Given a request is in the queue When I choose an Event Coordinator and assign Then exactly one Coordinator is assigned, the status becomes Under Review, the Coordinator and the Organiser are notified, the request leaves the queue, and the activity log records who assigned it and when
+Scenario 4 - Workload shown while choosing
+Given I am choosing a Coordinator When the list of Coordinators is shown Then each shows their count of active events, so the fewest-active-events rule the system used to apply (T-14) is available as advice without being enforced
+Scenario 5 - Only a Lead may assign from the queue
+Given I am an Event Coordinator or any role other than Event Coordinator Lead When I attempt to assign a queued request Then the action is refused and the refusal is recorded in the activity log
+Scenario 6 - Status transition and Organiser view unchanged
+Given a request has been assigned from the queue When the Organiser tracks the event (E03-S05) Then the status history shows Submitted followed by Under Review exactly as it did under automatic assignment, so E03-S01's delivered transition still holds
+Checklist
+- Confirm a newly submitted request has no Coordinator, stays Submitted and appears in the unassigned queue
+- Confirm the Lead is notified of each new queued request
+- See each queued request's basic information, oldest first, as a Lead only
+- Assign exactly one Coordinator from the queue, moving the event to Under Review with the Coordinator and Organiser notified and the action logged
+- See each Coordinator's active-event count while choosing
+- Be refused as a non-Lead when attempting to assign from the queue
+- Confirm the Submitted to Under Review transition recorded by E03-S01 is unchanged</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>C-69, T-70, T-72, T-73, T-74, O-35, O-38</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>E03-S09</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Reassign an event as the Lead</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead, I want to reassign an event to a different Event Coordinator where necessary so that workload, absences and conflicts can be managed without waiting on the current Coordinator.
+New story from the Week 7 Customer Changes (C-69). The Coordinator-initiated reassignment with acceptance delivered by E03-S01 Scenarios 3 to 6 stays in force (T-15 amended, not replaced). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lead reassignment takes effect immediately
+Given an event is assigned to a Coordinator When I, as the Lead, reassign it to another Coordinator Then the change takes effect at once without an acceptance step, the outgoing and incoming Coordinators and the Organiser are notified, and the activity log records who reassigned it and when (assumes O-36)
+Scenario 2 - Coordinator-initiated reassignment unchanged
+Given I am the assigned Coordinator and a reassignment has been agreed offline When I request reassignment to a named colleague Then E03-S01 Scenarios 3, 4 and 5 apply unchanged: I remain assigned until the colleague accepts, and a decline leaves me assigned
+Scenario 3 - Coordinator may ask the Lead to reassign
+Given I am the assigned Coordinator When I request reassignment without naming a colleague Then the request appears to the Lead with my reason, I remain assigned until the Lead acts, and the Lead may reassign (Scenario 1) or decline, which notifies me (assumes O-37)
+Scenario 4 - Only the assigned Coordinator or a Lead may reassign
+Given I am a Coordinator not assigned to the event When I attempt to reassign it Then the action is refused, exactly as in E03-S01 Scenario 6
+Checklist
+- Reassign an event directly as the Lead, with both Coordinators and the Organiser notified and the change logged
+- Confirm Coordinator-to-Coordinator reassignment still requires the colleague's acceptance
+- Ask the Lead to reassign my event without naming a colleague, and be told the outcome
+- Be refused when attempting to reassign an event I am not assigned to and am not the Lead for</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>C-69, C-56, T-15, T-70, T-73, T-74, O-36, O-37</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>E03-S10</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Oversee coordinator assignments and active events as the Lead</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator Lead, I want to view every coordinator assignment and every active event under my supervision so that I can see workload across the team and step in where needed.
+New story from the Week 7 Customer Changes (C-69). Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Every active event and its Coordinator listed
+Given events exist in every status When I open the oversight view Then every event whose status is Submitted, Under Review, Awaiting Clarification, Approved, Planning, Safety Review or Confirmed is listed with its assigned Coordinator or "Unassigned", and I can filter by Coordinator and by status
+Scenario 2 - Workload per Coordinator
+Given Coordinators have events assigned When I open the workload summary Then each Coordinator is shown with their count of active events and the list of those events
+Scenario 3 - One Lead sees everything
+Given there is one Event Coordinator Lead in Release 1 When I open the oversight view Then every assignment and active event is included regardless of which Coordinator holds it (assumes O-35)
+Scenario 4 - Coordinators cannot open the oversight view
+Given I am an Event Coordinator When I navigate to the oversight view Then access is refused and the attempt is recorded in the activity log
+Checklist
+- See every active event with its assigned Coordinator or Unassigned, filterable by Coordinator and status
+- See each Coordinator's active-event count and events
+- Confirm the view covers every assignment, not a subset
+- Be refused as a Coordinator</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>C-69, T-70, T-73, O-35</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E04-S01</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Record the event programme</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the programme for my event, including sessions and breaks, so that ConnectSphere can plan the venue and support around it.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Programme item added
 Given I am editing my event When I add a programme item with a title, start time and end time Then it appears in the event in chronological order
@@ -4328,39 +4850,39 @@
 Given two programme items overlap When I save them Then I am warned of the overlap</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more sessions so that each session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add sessions Then each session stores its own date, time, expected attendance, venue requirements and equipment requirements
@@ -4378,39 +4900,39 @@
 - See each session listed with its own venue booking and equipment status</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, T-48</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -4429,39 +4951,39 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -4477,39 +4999,39 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -4526,39 +5048,39 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -4574,40 +5096,40 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03 because that story is Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -4629,39 +5151,39 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -4682,39 +5204,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>B-08, C-65, T-66</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -4732,39 +5254,39 @@
 - Confirm suitability is advisory and does not itself block a booking request</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-21, B-08</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -4792,39 +5314,39 @@
 - View the status of each of my booking requests</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, O-27, O-29, O-30</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -4844,40 +5366,40 @@
 - Confirm the Coordinator is notified of either decision</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -4910,39 +5432,39 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -4963,39 +5485,39 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -5012,39 +5534,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -5060,39 +5582,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -5108,39 +5630,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -5159,39 +5681,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -5204,39 +5726,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -5252,39 +5774,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -5303,39 +5825,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -5343,39 +5865,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -5383,39 +5905,39 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event confirmed
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, and its full requested equipment is reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details (C-67, T-68; assumes O-28)
@@ -5438,39 +5960,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a confirmed event to planning when an arrangement breaks so that its status reflects reality.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reverted with a recorded reason
 Given an event is Confirmed When I revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -5486,39 +6008,39 @@
 - Confirm the reversion is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -5536,39 +6058,39 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -5589,39 +6111,39 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -5642,39 +6164,39 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -5693,39 +6215,39 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -5744,39 +6266,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -5788,39 +6310,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -5836,39 +6358,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -5886,39 +6408,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -5937,39 +6459,39 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
@@ -5990,39 +6512,39 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an event to new dates so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Date change flags bookings
 Given an event has a confirmed venue and equipment When I change its date Then the existing bookings are flagged as requiring reconfirmation and are not moved silently
@@ -6030,39 +6552,39 @@
 Given Attendees have registered for the event When it is rescheduled Then all registered Attendees are notified of the new date and time</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -6081,39 +6603,39 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my confirmed events so that I can arrange an alternative before Attendees are affected.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Blocked venue flags the event
 Given my event has a confirmed venue When Venue Staff block that venue over the event's period Then I am notified and the event is flagged as at risk
@@ -6121,39 +6643,39 @@
 Given my event is flagged as at risk When I open it Then the reason and the affected arrangement are shown and I can begin a new venue search from that screen</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -6181,39 +6703,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -6221,39 +6743,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -6261,39 +6783,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -6301,39 +6823,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -6343,39 +6865,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -6383,39 +6905,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -6423,39 +6945,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -6464,39 +6986,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -6506,39 +7028,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -6546,39 +7068,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -6586,39 +7108,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -6638,15 +7160,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -921,7 +921,7 @@
           <t>Scenario 1 - Lead lands on the unassigned queue
 Given I am a pre-seeded Event Coordinator Lead When I sign in with valid credentials Then I am taken to the unassigned queue (E03-S08) with the oversight view (E03-S10) one step away, and the navigation shows only the Lead's pages
 Scenario 2 - Safety Officer lands on the safety review queue
-Given I am a pre-seeded Safety Officer When I sign in with valid credentials Then I am taken to the list of events awaiting Operational Safety Check (E08-S07), and the navigation shows only the Safety Officer's pages
+Given I am a pre-seeded Safety Officer When I sign in with valid credentials Then I am taken to the list of events awaiting Operational Safety Check (E08-S06), and the navigation shows only the Safety Officer's pages
 Scenario 3 - One role per account
 Given a Lead or Safety Officer account exists When its role is inspected Then it holds exactly that one role and no Coordinator permissions, consistent with ADR-012 (assumes O-44)
 Scenario 4 - Existing roles' sign-in unchanged
@@ -2635,29 +2635,33 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.</t>
+          <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
+Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Scenario 1 - All arrangements complete, event confirmed
-Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, and its full requested equipment is reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details (C-67, T-68; assumes O-28)
-Scenario 2 - Missing venue blocks confirmation
-Given the event has no Confirmed venue booking, or any of its venue bookings is still Pending or Conflicting When I try to confirm Then confirmation is blocked and each outstanding booking is listed by venue (assumes O-28)
-Scenario 3 - Partial equipment blocks confirmation
-Given the event has only a partial equipment reservation When I try to confirm Then confirmation is blocked and the outstanding quantity is shown
+          <t>Scenario 1 - All arrangements complete, event submitted for safety review
+Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
+Scenario 2 - Missing venue blocks submission
+Given the event has no Confirmed venue booking, or any of its venue bookings is still Pending or Conflicting When I try to submit for safety review Then submission is blocked and each outstanding booking is listed by venue (assumes O-28)
+Scenario 3 - Partial equipment blocks submission
+Given the event has only a partial equipment reservation When I try to submit for safety review Then submission is blocked and the outstanding quantity is shown
 Scenario 4 - None required does not block
-Given the event was submitted with 'none required' for equipment When I confirm it Then that requirement counts as fulfilled and does not block confirmation
-Scenario 5 - Outstanding support assignment blocks confirmation
-Given the event requested technical support and no staff are assigned When I try to confirm Then confirmation is blocked
+Given the event was submitted with 'none required' for equipment When I submit it for safety review Then that requirement counts as fulfilled and does not block submission
+Scenario 5 - Outstanding support assignment blocks submission
+Given the event requested technical support and no staff are assigned When I try to submit for safety review Then submission is blocked
 Scenario 6 - Organiser sees confirmed arrangements
 Given an event has been confirmed When the Event Organiser views it Then every confirmed venue with its purpose and period, the date, time and arrangements are shown
-Checklist
-- Confirm an event that has a confirmed venue and full equipment reservation
-- Be blocked from confirming while the event has no Confirmed venue booking or any booking still Pending or Conflicting, with each one listed (assumes O-28)
-- Be blocked from confirming while an equipment reservation is partial, with the shortfall shown
+Scenario 7 - Confirmed is reached only through approval
+Given an event is in Safety Review When anyone other than a Safety Officer attempts to set its status to Confirmed Then the action is refused and recorded in the activity log (C-70, T-71)
+Checklist
+- Submit an event for its Operational Safety Check once every venue booking is Confirmed or withdrawn, equipment is fully reserved and technical support is assigned, moving it to Safety Review with the Safety Officer notified
+- Be blocked from submitting while the event has no Confirmed venue booking or any booking still Pending or Conflicting, with each one listed (assumes O-28)
+- Be blocked from submitting while an equipment reservation is partial, with the shortfall shown
 - Confirm an event whose equipment requirement was recorded as 'none required'
-- Be blocked from confirming while a requested technical support assignment is outstanding
+- Be blocked from submitting while a requested technical support assignment is outstanding
+- Confirm the event becomes Confirmed only through the Safety Officer's approval (E08-S06), never directly
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
@@ -2666,7 +2670,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28</t>
+          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2705,12 +2709,15 @@
 Given registered Attendees exist When the event is reverted Then they are notified that arrangements are being revised
 Scenario 3 - No automatic reversion
 Given an arrangement breaks on a confirmed event When no one reverts it Then the status stays Confirmed and the affected arrangement is flagged
+Scenario 4 - Reverted event passes the safety check again
+Given a Confirmed event has been reverted to Planning When its arrangements are complete again and it is resubmitted (E08-S03) Then it enters Safety Review and needs a fresh approval before it is Confirmed again; the earlier safety decision stays in the activity log but is not reused (C-70, T-71)
 Checklist
 - Revert a confirmed event to Planning with a recorded reason
 - Confirm the Organiser is notified with the reason
 - Confirm registered Attendees are notified
 - Confirm the status never reverts automatically
-- Confirm the reversion is recorded in the activity log</t>
+- Confirm the reversion is recorded in the activity log
+- Confirm a reverted event must pass the Operational Safety Check again before it is Confirmed again</t>
         </is>
       </c>
       <c r="G41" s="2" t="n">
@@ -2718,7 +2725,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>C-48, T-03, T-28</t>
+          <t>C-48, T-03, T-28, C-70, T-71</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2780,30 +2787,98 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>E08 Readiness &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Conduct the Operational Safety Check as the Safety Officer</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
+New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Events awaiting review listed with what the check needs
+Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
+Scenario 2 - Structured review of the listed factors
+Given I open an event from the queue When I conduct the check Then I record, for each of expected attendance against capacity, venue capacity and layout, emergency access, accessibility requirements, equipment placement, crowd movement and known venue restrictions, whether it is satisfactory, with a comment, before choosing an overall decision (assumes O-42)
+Scenario 3 - Approval confirms the event
+Given every factor is satisfactory When I approve Then the status becomes Confirmed, the Organiser and the Coordinator are notified with the confirmed details (E08-S03 Scenario 6 and E11-S01's "Event confirmed" row apply), and the activity log records my decision, my identity, the time and the completed checklist
+Scenario 4 - Requesting changes returns the event to planning
+Given one or more factors are unsatisfactory When I request changes and record which factors and why Then the status becomes Planning, the Coordinator and the Organiser are notified with the items to address, the affected venue or technical arrangements are flagged for re-review, the decision is logged, and the event cannot become Confirmed until it is resubmitted (E08-S03) and approved (assumes O-41)
+Scenario 5 - Rejecting the safety arrangement does not cancel the event
+Given the safety arrangement as a whole is unacceptable When I reject it and record the reason Then the status becomes Planning with a visible "safety arrangement rejected" flag and the reason, the Coordinator and the Organiser are notified, the event is not cancelled, and the Coordinator may rework and resubmit or cancel it through E10-S04 (assumes O-41)
+Scenario 6 - Reason required for reject or request changes
+Given I choose reject or request changes When I have not recorded a reason Then the decision is refused until I do
+Scenario 7 - Only a Safety Officer decides
+Given I am a Coordinator, an Event Coordinator Lead or any other role When I attempt to approve, reject or request changes on an event in Safety Review Then the action is refused and recorded in the activity log
+Scenario 8 - Events confirmed before this story are not re-reviewed
+Given an event was Confirmed before the Operational Safety Check existed When the check is introduced Then that event keeps its status, has no safety record and is not placed in Safety Review (assumes O-43)
+Scenario 9 - Status display and deactivation treat Safety Review as active
+Given an event is in Safety Review When its Organiser tracks it (E03-S05) Then "Safety Review" and the date it was reached are shown in plain language; and Given its Coordinator attempts to deactivate their account (E01-S11) Then Safety Review counts as an active-lifecycle status and deactivation is blocked (T-52)
+Scenario 10 - Every decision is auditable
+Given I approve, request changes or reject When the decision completes Then the activity log holds an entry with my identity, the action (safety check approved, changes requested or rejected), the event, the time and the checklist, immutable as E14-S02 requires
+Checklist
+- See every event awaiting its safety check with the information the listed factors need, oldest first
+- Record each factor as satisfactory or not, with a comment, before deciding
+- Approve an event, making it Confirmed with the Organiser and Coordinator notified
+- Request changes or reject with a mandatory reason, returning the event to Planning without cancelling it and flagging the affected arrangements
+- Be refused as any role other than Safety Officer
+- Confirm events already Confirmed before this story are untouched
+- Confirm the status tracker shows Safety Review and the deactivation block counts it
+- Confirm every decision is in the activity log</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -2824,43 +2899,43 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -2881,43 +2956,43 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -2936,43 +3011,43 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -2991,43 +3066,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -3039,43 +3114,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -3091,43 +3166,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -3145,43 +3220,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -3200,43 +3275,43 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
@@ -3257,43 +3332,43 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -3312,43 +3387,43 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3376,43 +3451,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -3432,15 +3507,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -3457,7 +3532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4065,7 +4140,7 @@
           <t>Scenario 1 - Lead lands on the unassigned queue
 Given I am a pre-seeded Event Coordinator Lead When I sign in with valid credentials Then I am taken to the unassigned queue (E03-S08) with the oversight view (E03-S10) one step away, and the navigation shows only the Lead's pages
 Scenario 2 - Safety Officer lands on the safety review queue
-Given I am a pre-seeded Safety Officer When I sign in with valid credentials Then I am taken to the list of events awaiting Operational Safety Check (E08-S07), and the navigation shows only the Safety Officer's pages
+Given I am a pre-seeded Safety Officer When I sign in with valid credentials Then I am taken to the list of events awaiting Operational Safety Check (E08-S06), and the navigation shows only the Safety Officer's pages
 Scenario 3 - One role per account
 Given a Lead or Safety Officer account exists When its role is inspected Then it holds exactly that one role and no Coordinator permissions, consistent with ADR-012 (assumes O-44)
 Scenario 4 - Existing roles' sign-in unchanged
@@ -5934,29 +6009,33 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.</t>
+          <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
+Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Scenario 1 - All arrangements complete, event confirmed
-Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, and its full requested equipment is reserved When I confirm the event Then the status becomes Confirmed and the Event Organiser is notified with the confirmed details (C-67, T-68; assumes O-28)
-Scenario 2 - Missing venue blocks confirmation
-Given the event has no Confirmed venue booking, or any of its venue bookings is still Pending or Conflicting When I try to confirm Then confirmation is blocked and each outstanding booking is listed by venue (assumes O-28)
-Scenario 3 - Partial equipment blocks confirmation
-Given the event has only a partial equipment reservation When I try to confirm Then confirmation is blocked and the outstanding quantity is shown
+          <t>Scenario 1 - All arrangements complete, event submitted for safety review
+Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
+Scenario 2 - Missing venue blocks submission
+Given the event has no Confirmed venue booking, or any of its venue bookings is still Pending or Conflicting When I try to submit for safety review Then submission is blocked and each outstanding booking is listed by venue (assumes O-28)
+Scenario 3 - Partial equipment blocks submission
+Given the event has only a partial equipment reservation When I try to submit for safety review Then submission is blocked and the outstanding quantity is shown
 Scenario 4 - None required does not block
-Given the event was submitted with 'none required' for equipment When I confirm it Then that requirement counts as fulfilled and does not block confirmation
-Scenario 5 - Outstanding support assignment blocks confirmation
-Given the event requested technical support and no staff are assigned When I try to confirm Then confirmation is blocked
+Given the event was submitted with 'none required' for equipment When I submit it for safety review Then that requirement counts as fulfilled and does not block submission
+Scenario 5 - Outstanding support assignment blocks submission
+Given the event requested technical support and no staff are assigned When I try to submit for safety review Then submission is blocked
 Scenario 6 - Organiser sees confirmed arrangements
 Given an event has been confirmed When the Event Organiser views it Then every confirmed venue with its purpose and period, the date, time and arrangements are shown
-Checklist
-- Confirm an event that has a confirmed venue and full equipment reservation
-- Be blocked from confirming while the event has no Confirmed venue booking or any booking still Pending or Conflicting, with each one listed (assumes O-28)
-- Be blocked from confirming while an equipment reservation is partial, with the shortfall shown
+Scenario 7 - Confirmed is reached only through approval
+Given an event is in Safety Review When anyone other than a Safety Officer attempts to set its status to Confirmed Then the action is refused and recorded in the activity log (C-70, T-71)
+Checklist
+- Submit an event for its Operational Safety Check once every venue booking is Confirmed or withdrawn, equipment is fully reserved and technical support is assigned, moving it to Safety Review with the Safety Officer notified
+- Be blocked from submitting while the event has no Confirmed venue booking or any booking still Pending or Conflicting, with each one listed (assumes O-28)
+- Be blocked from submitting while an equipment reservation is partial, with the shortfall shown
 - Confirm an event whose equipment requirement was recorded as 'none required'
-- Be blocked from confirming while a requested technical support assignment is outstanding
+- Be blocked from submitting while a requested technical support assignment is outstanding
+- Confirm the event becomes Confirmed only through the Safety Officer's approval (E08-S06), never directly
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
@@ -5965,7 +6044,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28</t>
+          <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -6000,12 +6079,15 @@
 Given registered Attendees exist When the event is reverted Then they are notified that arrangements are being revised
 Scenario 3 - No automatic reversion
 Given an arrangement breaks on a confirmed event When no one reverts it Then the status stays Confirmed and the affected arrangement is flagged
+Scenario 4 - Reverted event passes the safety check again
+Given a Confirmed event has been reverted to Planning When its arrangements are complete again and it is resubmitted (E08-S03) Then it enters Safety Review and needs a fresh approval before it is Confirmed again; the earlier safety decision stays in the activity log but is not reused (C-70, T-71)
 Checklist
 - Revert a confirmed event to Planning with a recorded reason
 - Confirm the Organiser is notified with the reason
 - Confirm registered Attendees are notified
 - Confirm the status never reverts automatically
-- Confirm the reversion is recorded in the activity log</t>
+- Confirm the reversion is recorded in the activity log
+- Confirm a reverted event must pass the Operational Safety Check again before it is Confirmed again</t>
         </is>
       </c>
       <c r="G52" s="2" t="n">
@@ -6013,7 +6095,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>C-48, T-03, T-28</t>
+          <t>C-48, T-03, T-28, C-70, T-71</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -6072,25 +6154,89 @@
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>E08 Readiness &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Conduct the Operational Safety Check as the Safety Officer</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
+New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Events awaiting review listed with what the check needs
+Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
+Scenario 2 - Structured review of the listed factors
+Given I open an event from the queue When I conduct the check Then I record, for each of expected attendance against capacity, venue capacity and layout, emergency access, accessibility requirements, equipment placement, crowd movement and known venue restrictions, whether it is satisfactory, with a comment, before choosing an overall decision (assumes O-42)
+Scenario 3 - Approval confirms the event
+Given every factor is satisfactory When I approve Then the status becomes Confirmed, the Organiser and the Coordinator are notified with the confirmed details (E08-S03 Scenario 6 and E11-S01's "Event confirmed" row apply), and the activity log records my decision, my identity, the time and the completed checklist
+Scenario 4 - Requesting changes returns the event to planning
+Given one or more factors are unsatisfactory When I request changes and record which factors and why Then the status becomes Planning, the Coordinator and the Organiser are notified with the items to address, the affected venue or technical arrangements are flagged for re-review, the decision is logged, and the event cannot become Confirmed until it is resubmitted (E08-S03) and approved (assumes O-41)
+Scenario 5 - Rejecting the safety arrangement does not cancel the event
+Given the safety arrangement as a whole is unacceptable When I reject it and record the reason Then the status becomes Planning with a visible "safety arrangement rejected" flag and the reason, the Coordinator and the Organiser are notified, the event is not cancelled, and the Coordinator may rework and resubmit or cancel it through E10-S04 (assumes O-41)
+Scenario 6 - Reason required for reject or request changes
+Given I choose reject or request changes When I have not recorded a reason Then the decision is refused until I do
+Scenario 7 - Only a Safety Officer decides
+Given I am a Coordinator, an Event Coordinator Lead or any other role When I attempt to approve, reject or request changes on an event in Safety Review Then the action is refused and recorded in the activity log
+Scenario 8 - Events confirmed before this story are not re-reviewed
+Given an event was Confirmed before the Operational Safety Check existed When the check is introduced Then that event keeps its status, has no safety record and is not placed in Safety Review (assumes O-43)
+Scenario 9 - Status display and deactivation treat Safety Review as active
+Given an event is in Safety Review When its Organiser tracks it (E03-S05) Then "Safety Review" and the date it was reached are shown in plain language; and Given its Coordinator attempts to deactivate their account (E01-S11) Then Safety Review counts as an active-lifecycle status and deactivation is blocked (T-52)
+Scenario 10 - Every decision is auditable
+Given I approve, request changes or reject When the decision completes Then the activity log holds an entry with my identity, the action (safety check approved, changes requested or rejected), the event, the time and the checklist, immutable as E14-S02 requires
+Checklist
+- See every event awaiting its safety check with the information the listed factors need, oldest first
+- Record each factor as satisfactory or not, with a comment, before deciding
+- Approve an event, making it Confirmed with the Organiser and Coordinator notified
+- Request changes or reject with a mandatory reason, returning the event to Planning without cancelling it and flagging the affected arrangements
+- Be refused as any role other than Safety Officer
+- Confirm events already Confirmed before this story are untouched
+- Confirm the status tracker shows Safety Review and the deactivation block counts it
+- Confirm every decision is in the activity log</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -6111,39 +6257,39 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -6164,39 +6310,39 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -6215,39 +6361,39 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -6266,39 +6412,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -6310,39 +6456,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -6358,39 +6504,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -6408,39 +6554,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -6459,39 +6605,39 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
@@ -6512,39 +6658,39 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an event to new dates so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Date change flags bookings
 Given an event has a confirmed venue and equipment When I change its date Then the existing bookings are flagged as requiring reconfirmation and are not moved silently
@@ -6552,39 +6698,39 @@
 Given Attendees have registered for the event When it is rescheduled Then all registered Attendees are notified of the new date and time</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -6603,39 +6749,39 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my confirmed events so that I can arrange an alternative before Attendees are affected.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Blocked venue flags the event
 Given my event has a confirmed venue When Venue Staff block that venue over the event's period Then I am notified and the event is flagged as at risk
@@ -6643,39 +6789,39 @@
 Given my event is flagged as at risk When I open it Then the reason and the affected arrangement are shown and I can begin a new venue search from that screen</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -6703,39 +6849,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -6743,39 +6889,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -6783,39 +6929,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -6823,39 +6969,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -6865,39 +7011,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -6905,39 +7051,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -6945,39 +7091,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -6986,39 +7132,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -7028,39 +7174,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -7068,39 +7214,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -7108,39 +7254,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -7160,15 +7306,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1889,30 +1889,89 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>E05 Venue Catalogue &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Mark a venue temporarily unavailable over existing bookings</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
+New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Unavailability recorded with a reason
+Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
+Scenario 2 - Overlapping bookings become Conflicting, not released
+Given the venue has a Pending request and a Confirmed booking inside the period When I save the unavailability Then the save succeeds, both bookings are marked Conflicting, neither is released or cancelled, and the two affected events are listed to me on save
+Scenario 3 - The event itself is untouched
+Given a Confirmed event's booking has just become Conflicting When anyone views that event Then its status is still Confirmed, every other arrangement is intact, and a venue-conflict flag with the reason category is shown; the event changes status only when its Coordinator acts (assumes O-24)
+Scenario 4 - Affected Coordinators informed
+Given the unavailability made one or more bookings Conflicting When it is saved Then the Coordinator of each affected event receives an in-app and email notification naming the venue, the period, the reason category and the event, and stating that alternative arrangements are required (assumes O-25)
+Scenario 5 - End date required and extendable
+Given I am recording an unavailability When I omit the end date and time Then the save is refused; and Given a saved unavailability When I extend its end Then bookings newly inside the longer period are handled as in Scenario 2 (assumes O-23)
+Scenario 6 - Unavailability shortened or ended early
+Given a booking is Conflicting only because of an unavailability When I shorten or end that unavailability so the booking no longer overlaps it Then the Conflicting flag clears and the booking stands as it was; a booking the Coordinator has already cancelled or replaced is not restored (assumes O-26)
+Checklist
+- Mark a venue unavailable for a period with a reason category and a note, including when Pending or Confirmed bookings fall inside the period
+- See the affected events listed on save and their bookings marked Conflicting, with none released or cancelled
+- Confirm the affected events keep their status and other arrangements, with a visible venue-conflict flag
+- Confirm each affected Coordinator is notified in-app and by email
+- Be refused an unavailability with no end date and time
+- Confirm shortening or ending an unavailability clears the Conflicting flag on bookings it no longer touches
+- Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -1933,43 +1992,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>B-08, C-65, T-66</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -1987,43 +2046,43 @@
 - Confirm suitability is advisory and does not itself block a booking request</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-21, B-08</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -2051,43 +2110,43 @@
 - View the status of each of my booking requests</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, O-27, O-29, O-30</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -2107,44 +2166,44 @@
 - Confirm the Coordinator is notified of either decision</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -2177,43 +2236,43 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -2234,43 +2293,43 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -2287,43 +2346,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2339,43 +2398,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2391,43 +2450,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2446,43 +2505,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2495,43 +2554,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2547,43 +2606,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2602,44 +2661,44 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -2665,43 +2724,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a confirmed event to planning when an arrangement breaks so that its status reflects reality.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reverted with a recorded reason
 Given an event is Confirmed When I revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -2720,43 +2779,43 @@
 - Confirm a reverted event must pass the Operational Safety Check again before it is Confirmed again</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -2774,44 +2833,44 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -2844,41 +2903,41 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -2899,43 +2958,43 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -2956,43 +3015,43 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -3011,43 +3070,43 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -3066,43 +3125,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -3114,43 +3173,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -3166,43 +3225,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -3220,43 +3279,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -3275,43 +3334,43 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
@@ -3332,43 +3391,43 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -3387,43 +3446,98 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>E10 Changes, Rescheduling &amp; Cancellation</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Handle a venue lost from a confirmed event</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lost venue flags the event
+Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
+Scenario 2 - Flagged event offers a replacement search
+Given my event is flagged When I open it Then the reason category, the period and the affected booking are shown, the original venue, dates and requirements are preserved, and I can start a venue search (E06-S01) for the same event from that screen
+Scenario 3 - Replacement requested without losing the original
+Given I have found a replacement venue When I submit a booking request for it (E06-S03) Then the request is created for the same event alongside the Conflicting booking, and I may cancel the Conflicting booking explicitly once the replacement is Confirmed; nothing is cancelled for me
+Scenario 4 - Organiser and Attendees told on the actual change
+Given I confirm a replacement venue When the venue of a Confirmed event changes Then the Organiser and registered Attendees are notified of the new venue through the existing venue-change routing (E11-S01), and not earlier (assumes O-25)
+Checklist
+- Be notified when a venue I have booked is marked unavailable over my booking
+- See the reason, period and affected booking on the event, with the original event information intact
+- Start a venue search for the same event from the flagged event
+- Request a replacement venue while the Conflicting booking remains on the event until I cancel it
+- Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3451,43 +3565,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -3507,15 +3621,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -3532,7 +3646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5240,25 +5354,80 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>E05 Venue Catalogue &amp; Availability</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Mark a venue temporarily unavailable over existing bookings</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
+New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Unavailability recorded with a reason
+Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
+Scenario 2 - Overlapping bookings become Conflicting, not released
+Given the venue has a Pending request and a Confirmed booking inside the period When I save the unavailability Then the save succeeds, both bookings are marked Conflicting, neither is released or cancelled, and the two affected events are listed to me on save
+Scenario 3 - The event itself is untouched
+Given a Confirmed event's booking has just become Conflicting When anyone views that event Then its status is still Confirmed, every other arrangement is intact, and a venue-conflict flag with the reason category is shown; the event changes status only when its Coordinator acts (assumes O-24)
+Scenario 4 - Affected Coordinators informed
+Given the unavailability made one or more bookings Conflicting When it is saved Then the Coordinator of each affected event receives an in-app and email notification naming the venue, the period, the reason category and the event, and stating that alternative arrangements are required (assumes O-25)
+Scenario 5 - End date required and extendable
+Given I am recording an unavailability When I omit the end date and time Then the save is refused; and Given a saved unavailability When I extend its end Then bookings newly inside the longer period are handled as in Scenario 2 (assumes O-23)
+Scenario 6 - Unavailability shortened or ended early
+Given a booking is Conflicting only because of an unavailability When I shorten or end that unavailability so the booking no longer overlaps it Then the Conflicting flag clears and the booking stands as it was; a booking the Coordinator has already cancelled or replaced is not restored (assumes O-26)
+Checklist
+- Mark a venue unavailable for a period with a reason category and a note, including when Pending or Confirmed bookings fall inside the period
+- See the affected events listed on save and their bookings marked Conflicting, with none released or cancelled
+- Confirm the affected events keep their status and other arrangements, with a visible venue-conflict flag
+- Confirm each affected Coordinator is notified in-app and by email
+- Be refused an unavailability with no end date and time
+- Confirm shortening or ending an unavailability clears the Conflicting flag on bookings it no longer touches
+- Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -5279,39 +5448,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>B-08, C-65, T-66</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -5329,39 +5498,39 @@
 - Confirm suitability is advisory and does not itself block a booking request</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-21, B-08</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -5389,39 +5558,39 @@
 - View the status of each of my booking requests</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, O-27, O-29, O-30</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -5441,40 +5610,40 @@
 - Confirm the Coordinator is notified of either decision</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -5507,39 +5676,39 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -5560,39 +5729,39 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -5609,39 +5778,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -5657,39 +5826,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -5705,39 +5874,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -5756,39 +5925,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -5801,39 +5970,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -5849,39 +6018,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -5900,39 +6069,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -5940,39 +6109,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -5980,40 +6149,40 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -6039,39 +6208,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to return a confirmed event to planning when an arrangement breaks so that its status reflects reality.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reverted with a recorded reason
 Given an event is Confirmed When I revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -6090,39 +6259,39 @@
 - Confirm a reverted event must pass the Operational Safety Check again before it is Confirmed again</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -6140,40 +6309,40 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -6206,37 +6375,37 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register for a confirmed event so that my place is reserved and I receive the event information.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open event
 Given an event is Confirmed, registration is open and places remain When I submit the required registration information Then my place is reserved and I receive a confirmation containing the event details
@@ -6257,39 +6426,39 @@
 - Be refused registration for an event that is not Confirmed</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-35, T-48, C-67, T-68, O-30</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want registration to stop at the booked venue's capacity so that more people do not register than the venue can hold.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue capacity enforced
 Given the event's capacity is the booked venue's capacity When registrations reach that number Then further registrations are refused
@@ -6310,39 +6479,39 @@
 - Confirm a manual addition is distinguishable from a normal registration</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, T-30, T-31, T-50, B-11</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set when registration opens and closes, and when withdrawal closes, so that Attendees can act only during the permitted windows.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the registration opening date has not been reached When an Attendee views the event Then registration is shown as not yet open and the opening date is stated
@@ -6361,39 +6530,39 @@
 - Be warned when setting a closing date after the event has started</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given an event is full and the waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released
@@ -6412,39 +6581,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my registration so that my place is released to someone else.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn
 Given I am registered and the withdrawal deadline has not passed When I withdraw Then my registration is cancelled and the place becomes available again
@@ -6456,39 +6625,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -6504,39 +6673,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -6554,39 +6723,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the event
@@ -6605,39 +6774,39 @@
 - Be notified when the Coordinator approves or declines the request</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, T-16</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to tell me when a change affects arrangements already confirmed so that I re-check them rather than assuming they still hold.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance beyond capacity flagged
 Given an event has one or more confirmed venue bookings When its expected attendance is increased Then each venue booking whose governing headcount (the booking's own headcount where set, otherwise the event's attendance) now exceeds that venue's capacity is flagged for review, and the others are not (C-67; assumes O-27) and the Venue Staff are notified
@@ -6658,39 +6827,39 @@
 - Confirm affected Venue Staff and Technical Support Staff are notified</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an event to new dates so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Date change flags bookings
 Given an event has a confirmed venue and equipment When I change its date Then the existing bookings are flagged as requiring reconfirmation and are not moved silently
@@ -6698,39 +6867,39 @@
 Given Attendees have registered for the event When it is rescheduled Then all registered Attendees are notified of the new date and time</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an event and release its arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled, arrangements released
 Given an Event Organiser requests cancellation When I cancel the event and record a reason Then its status becomes Cancelled, its venue booking and equipment reservations are released, the venue calendar is updated and the affected staff are notified
@@ -6749,52 +6918,12 @@
 - Confirm a cancelled event is read-only and shows its reason and date</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, T-07, T-48</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>E10 Changes, Rescheduling &amp; Cancellation</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>E10-S05</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Handle a venue lost from a confirmed event</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my confirmed events so that I can arrange an alternative before Attendees are affected.</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Scenario 1 - Blocked venue flags the event
-Given my event has a confirmed venue When Venue Staff block that venue over the event's period Then I am notified and the event is flagged as at risk
-Scenario 2 - At-risk event offers a new search
-Given my event is flagged as at risk When I open it Then the reason and the affected arrangement are shown and I can begin a new venue search from that screen</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -6803,25 +6932,76 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
+          <t>E10 Changes, Rescheduling &amp; Cancellation</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Handle a venue lost from a confirmed event</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
+Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Lost venue flags the event
+Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
+Scenario 2 - Flagged event offers a replacement search
+Given my event is flagged When I open it Then the reason category, the period and the affected booking are shown, the original venue, dates and requirements are preserved, and I can start a venue search (E06-S01) for the same event from that screen
+Scenario 3 - Replacement requested without losing the original
+Given I have found a replacement venue When I submit a booking request for it (E06-S03) Then the request is created for the same event alongside the Conflicting booking, and I may cancel the Conflicting booking explicitly once the replacement is Confirmed; nothing is cancelled for me
+Scenario 4 - Organiser and Attendees told on the actual change
+Given I confirm a replacement venue When the venue of a Confirmed event changes Then the Organiser and registered Attendees are notified of the new venue through the existing venue-change routing (E11-S01), and not earlier (assumes O-25)
+Checklist
+- Be notified when a venue I have booked is marked unavailable over my booking
+- See the reason, period and affected booking on the event, with the original event information intact
+- Start a venue search for the same event from the flagged event
+- Request a replacement venue while the Conflicting booking remains on the event until I cancel it
+- Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -6849,39 +7029,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -6889,39 +7069,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -6929,39 +7109,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -6969,39 +7149,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -7011,39 +7191,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -7051,39 +7231,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -7091,39 +7271,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -7132,39 +7312,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -7174,39 +7354,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -7214,39 +7394,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -7254,39 +7434,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
@@ -7306,15 +7486,15 @@
 - Confirm log entries cannot be edited or deleted by any user</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>T-04</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -1851,7 +1851,7 @@
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
-Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03 because that story is Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
+Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1868,6 +1868,8 @@
 Given a venue has a maintenance block ending at 12:00 and a setup time of 30 minutes When a booking request for 12:00 to 14:00 is evaluated Then the block and the booking are compared on the booking's advertised times, so the request is not in conflict with the block (assumes O-22)
 Scenario 6 - Adjacent buffered windows do not conflict
 Given booking A occupies a venue until 12:45 once its turnaround is applied When booking B's buffered window on the same venue starts at exactly 12:45 Then there is no conflict, and when it starts at 12:44 there is
+Scenario 7 - Buffered occupancy excludes a venue from search
+Given a venue's existing booking or hold, once that venue's setup and turnaround time are applied, overlaps an event's requested period When a Coordinator runs the venue search for that event Then the venue does not appear as available even though the advertised event times do not overlap; E06-S01 is Done and is not edited, this is its buffered-search requirement placed here under T-74
 Checklist
 - Record a setup time and a turnaround time in whole minutes for each venue, with 0 allowed and 0 the default for existing venues
 - See both values on the venue's detail
@@ -1981,8 +1983,6 @@
 Given a venue is available but its capacity is below the event's expected attendance When results are displayed Then it is excluded or clearly marked as unsuitable
 Scenario 4 - Blocked or booked venues excluded
 Given a venue is blocked or already confirmed the event's period When I run the search Then it does not appear as available
-Scenario 5 - Buffered occupancy excludes a venue
-Given a venue's existing booking or hold, once that venue's setup and turnaround time are applied, overlaps the event's requested period When I run the search Then the venue does not appear as available even though the advertised event times do not overlap (C-65, T-66)
 Checklist
 - Search by date, time, expected attendance, location, capacity, accessibility, layout and required facilities
 - See matching venues with their capacity, layouts and facilities
@@ -1997,7 +1997,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>B-08, C-65, T-66</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -5315,7 +5315,7 @@
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
-Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03 because that story is Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
+Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -5332,6 +5332,8 @@
 Given a venue has a maintenance block ending at 12:00 and a setup time of 30 minutes When a booking request for 12:00 to 14:00 is evaluated Then the block and the booking are compared on the booking's advertised times, so the request is not in conflict with the block (assumes O-22)
 Scenario 6 - Adjacent buffered windows do not conflict
 Given booking A occupies a venue until 12:45 once its turnaround is applied When booking B's buffered window on the same venue starts at exactly 12:45 Then there is no conflict, and when it starts at 12:44 there is
+Scenario 7 - Buffered occupancy excludes a venue from search
+Given a venue's existing booking or hold, once that venue's setup and turnaround time are applied, overlaps an event's requested period When a Coordinator runs the venue search for that event Then the venue does not appear as available even though the advertised event times do not overlap; E06-S01 is Done and is not edited, this is its buffered-search requirement placed here under T-74
 Checklist
 - Record a setup time and a turnaround time in whole minutes for each venue, with 0 allowed and 0 the default for existing venues
 - See both values on the venue's detail
@@ -5437,8 +5439,6 @@
 Given a venue is available but its capacity is below the event's expected attendance When results are displayed Then it is excluded or clearly marked as unsuitable
 Scenario 4 - Blocked or booked venues excluded
 Given a venue is blocked or already confirmed the event's period When I run the search Then it does not appear as available
-Scenario 5 - Buffered occupancy excludes a venue
-Given a venue's existing booking or hold, once that venue's setup and turnaround time are applied, overlaps the event's requested period When I run the search Then the venue does not appear as available even though the advertised event times do not overlap (C-65, T-66)
 Checklist
 - Search by date, time, expected attendance, location, capacity, accessibility, layout and required facilities
 - See matching venues with their capacity, layouts and facilities
@@ -5453,7 +5453,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>B-08, C-65, T-66</t>
+          <t>B-08</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 031026.xlsx
@@ -2156,6 +2156,8 @@
 Given I attempt to reject without recording a reason When I confirm Then the rejection is blocked
 Scenario 4 - Approval checks the buffered window
 Given approving a pending request would make its buffered occupancy window overlap another Confirmed booking's buffered window on the same venue When I approve it Then approval is blocked and the conflicting booking is identified, even if the two advertised event times do not overlap (C-65, T-66)
+Scenario 5 - Booking decision recorded
+Given a venue booking is approved, rejected or released When the action completes Then an entry is recorded with the actor, the action, the affected records and the time
 Checklist
 - Approve a pending booking request for a free venue
 - Confirm the booking becomes Confirmed and the calendar updates
@@ -2163,7 +2165,9 @@
 - Be blocked from rejecting without a reason
 - Suggest an alternative venue alongside a rejection
 - Confirm the Coordinator can amend the request to the suggested venue without starting a new search
-- Confirm the Coordinator is notified of either decision</t>
+- Confirm the Coordinator is notified of either decision
+- Record each booking approval, rejection and release with actor, action, affected booking/event and time in the same transaction as the action
+- Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
@@ -2171,10 +2175,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>C-08, T-39, C-65, T-66</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
+          <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Le Xin</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3578,7 +3586,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3604,11 +3612,11 @@
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
-Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
+Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log
 Scenario 2 - Access denial recorded
 Given a user is denied access to an event or screen When the refusal occurs Then an entry is recorded with the user, the target and the time
-Scenario 3 - Booking decision recorded
-Given a venue booking is approved, rejected or released When the action completes Then an entry is recorded with the actor, the action, the affected records and the time
+Scenario 3 - Transferred to E06-S04 Scenario 5 (T-76)
+Booking approval, rejection and release logging is accepted under E06-S04. This historical scenario number is retained for traceability and is not an E14-S02 completion criterion.
 Scenario 4 - Deactivation recorded
 Given an account is deactivated When the action completes Then an entry is recorded
 Scenario 5 - Log entries immutable
@@ -3616,9 +3624,10 @@
 Checklist
 - Record every event status change with actor, action, event and time
 - Record every denied access attempt with user, target and time
-- Record every venue booking approval, rejection and release
 - Record every account deactivation
-- Confirm log entries cannot be edited or deleted by any user</t>
+- Confirm log entries cannot be edited or deleted by any user
+- Verify that an Event Coordinator can read the event Activity log within existing event access rules
+- Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
       <c r="G57" s="2" t="n">
@@ -3626,7 +3635,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-04, T-75, T-76</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -5600,6 +5609,8 @@
 Given I attempt to reject without recording a reason When I confirm Then the rejection is blocked
 Scenario 4 - Approval checks the buffered window
 Given approving a pending request would make its buffered occupancy window overlap another Confirmed booking's buffered window on the same venue When I approve it Then approval is blocked and the conflicting booking is identified, even if the two advertised event times do not overlap (C-65, T-66)
+Scenario 5 - Booking decision recorded
+Given a venue booking is approved, rejected or released When the action completes Then an entry is recorded with the actor, the action, the affected records and the time
 Checklist
 - Approve a pending booking request for a free venue
 - Confirm the booking becomes Confirmed and the calendar updates
@@ -5607,7 +5618,9 @@
 - Be blocked from rejecting without a reason
 - Suggest an alternative venue alongside a rejection
 - Confirm the Coordinator can amend the request to the suggested venue without starting a new search
-- Confirm the Coordinator is notified of either decision</t>
+- Confirm the Coordinator is notified of either decision
+- Record each booking approval, rejection and release with actor, action, affected booking/event and time in the same transaction as the action
+- Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -5615,7 +5628,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>C-08, T-39, C-65, T-66</t>
+          <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -7469,11 +7482,11 @@
       <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
-Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time
+Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log
 Scenario 2 - Access denial recorded
 Given a user is denied access to an event or screen When the refusal occurs Then an entry is recorded with the user, the target and the time
-Scenario 3 - Booking decision recorded
-Given a venue booking is approved, rejected or released When the action completes Then an entry is recorded with the actor, the action, the affected records and the time
+Scenario 3 - Transferred to E06-S04 Scenario 5 (T-76)
+Booking approval, rejection and release logging is accepted under E06-S04. This historical scenario number is retained for traceability and is not an E14-S02 completion criterion.
 Scenario 4 - Deactivation recorded
 Given an account is deactivated When the action completes Then an entry is recorded
 Scenario 5 - Log entries immutable
@@ -7481,9 +7494,10 @@
 Checklist
 - Record every event status change with actor, action, event and time
 - Record every denied access attempt with user, target and time
-- Record every venue booking approval, rejection and release
 - Record every account deactivation
-- Confirm log entries cannot be edited or deleted by any user</t>
+- Confirm log entries cannot be edited or deleted by any user
+- Verify that an Event Coordinator can read the event Activity log within existing event access rules
+- Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
       <c r="G79" s="2" t="n">
@@ -7491,7 +7505,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-04, T-75, T-76</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
